--- a/Översikt TIDAHOLM.xlsx
+++ b/Översikt TIDAHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45534</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>44637</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>44902</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>46262</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>43986</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44607</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>45183</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>44930</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>46279</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44607</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>44512</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>44512</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>44865</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>45246</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>45232</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45899</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>45925</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45930</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>46055</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>45684</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>44637</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>45322</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>44607</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3331,7 +3331,7 @@
         <v>44607</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>44607</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>46064</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>44519</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
         <v>44481</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>44573</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3875,7 +3875,7 @@
         <v>44783</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3953,7 +3953,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         <v>44529</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         <v>44550</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4250,7 +4250,7 @@
         <v>44832</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>44594</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>44630</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>44615</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>44508</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         <v>44462</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>44694</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>44512</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>44587</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>44889</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>44783</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>44546</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>44573</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>44703</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>44869</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5350,7 +5350,7 @@
         <v>44613</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         <v>44526</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         <v>44615</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>44474</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5647,7 +5647,7 @@
         <v>44623</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>44686</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         <v>44615</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>44615</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>44522</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6012,7 +6012,7 @@
         <v>44589</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6085,7 +6085,7 @@
         <v>44615</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6158,7 +6158,7 @@
         <v>44588</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>44511</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>44550</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>44550</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>44550</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         <v>44860</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>44812</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>44817</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         <v>44580</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>44719</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6888,7 +6888,7 @@
         <v>45425</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6961,7 +6961,7 @@
         <v>44693</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>45266</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         <v>45267</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7180,7 +7180,7 @@
         <v>44559</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>45758</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7326,7 +7326,7 @@
         <v>44903</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         <v>44900</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>45483</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>44817</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7623,7 +7623,7 @@
         <v>45099</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>45099</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>45103</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>45643</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7930,7 +7930,7 @@
         <v>45721</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         <v>45580</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8076,7 +8076,7 @@
         <v>44610</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8149,7 +8149,7 @@
         <v>45120</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>45041</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         <v>45534</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8373,7 +8373,7 @@
         <v>45016</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         <v>45167</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8519,7 +8519,7 @@
         <v>44860</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8592,7 +8592,7 @@
         <v>45420</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>45314</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>45103</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         <v>45335</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>45481</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>45232</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         <v>44476</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         <v>44636</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         <v>45687</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9259,7 +9259,7 @@
         <v>45146</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>45068</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9405,7 +9405,7 @@
         <v>45637</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>45204</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>45443</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>45637</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>44831</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>44720</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>45623</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>45215</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>45212</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>45280</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
         <v>45336</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>45356</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         <v>45105</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>45359</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10432,7 +10432,7 @@
         <v>45581</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
         <v>45103</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10583,7 +10583,7 @@
         <v>45548</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>45183</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>44945</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>45556</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10880,7 +10880,7 @@
         <v>44817</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>45884</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11031,7 +11031,7 @@
         <v>45669</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>45784</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>45672</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>45875</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>44783</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
         <v>45811</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>45232</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>45891</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>45098</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>45919</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>45462</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         <v>45897</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>45911</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>45899</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>45006</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>45630</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>44900</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12287,7 +12287,7 @@
         <v>44900</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>45779</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12438,7 +12438,7 @@
         <v>45790</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>45904</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>45904</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>45904</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>45904</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>45904</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>44622</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>45608</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>45847</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>45665</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>45919</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>45477</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13339,7 +13339,7 @@
         <v>45576</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>45282</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>45474</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>45930</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>45930</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13719,7 +13719,7 @@
         <v>45930</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13797,7 +13797,7 @@
         <v>45121</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>45930</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>45930</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14031,7 +14031,7 @@
         <v>45931</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>45580</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>44900</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>45709</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>45937</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>45358</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>45358</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>45576</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>45156</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14693,7 +14693,7 @@
         <v>45539</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>44973</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>44580</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14912,7 +14912,7 @@
         <v>45232</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>46153</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>45105</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>46153</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>45030</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>45965</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
         <v>45967</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15438,7 +15438,7 @@
         <v>45967</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         <v>45967</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15594,7 +15594,7 @@
         <v>45967</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>45469</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15750,7 +15750,7 @@
         <v>45469</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>45967</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>45469</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15984,7 +15984,7 @@
         <v>45967</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>45967</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>44529</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>45967</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
         <v>45362</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44973</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>45968</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>44806</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>45596</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>45352</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>45603</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>45603</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>45530</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>45443</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>45979</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>45981</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         <v>44630</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         <v>45985</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>45530</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>44910</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>45594</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>45814</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>45392</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>45096</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>45414</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>45951</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>45911</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         <v>44552</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>45469</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>46006</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>44546</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>46013</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18360,7 +18360,7 @@
         <v>45404</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18433,7 +18433,7 @@
         <v>45048</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18506,7 +18506,7 @@
         <v>46021</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>45000</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18652,7 +18652,7 @@
         <v>45013</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18725,7 +18725,7 @@
         <v>44685</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         <v>45047</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18871,7 +18871,7 @@
         <v>45204</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18944,7 +18944,7 @@
         <v>45469</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19022,7 +19022,7 @@
         <v>45469</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19100,7 +19100,7 @@
         <v>45311</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19173,7 +19173,7 @@
         <v>44958</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>45240</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19324,7 +19324,7 @@
         <v>45147</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19397,7 +19397,7 @@
         <v>45576</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>46043</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         <v>45628</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19616,7 +19616,7 @@
         <v>44930</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19689,7 +19689,7 @@
         <v>46042</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19762,7 +19762,7 @@
         <v>46044</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19835,7 +19835,7 @@
         <v>44973</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
         <v>46175</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19986,7 +19986,7 @@
         <v>46175</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>46175</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20132,7 +20132,7 @@
         <v>44915</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20210,7 +20210,7 @@
         <v>44915</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20288,7 +20288,7 @@
         <v>44911</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20366,7 +20366,7 @@
         <v>45469</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>46051</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20522,7 +20522,7 @@
         <v>46178</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>46059</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>44501</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>46064</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>46181</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>44972</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>46181</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>44766</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21116,7 +21116,7 @@
         <v>45594</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>46080</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>46079</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21335,7 +21335,7 @@
         <v>46080</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>46084</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>46084</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>46084</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21627,7 +21627,7 @@
         <v>45238</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>45373</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>44865</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21846,7 +21846,7 @@
         <v>45070</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>45155</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21997,7 +21997,7 @@
         <v>44900</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22075,7 +22075,7 @@
         <v>45225</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22148,7 +22148,7 @@
         <v>45587</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>45007</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>46191</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         <v>46181</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>44985</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>45257</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22591,7 +22591,7 @@
         <v>46105</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22664,7 +22664,7 @@
         <v>46105</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22737,7 +22737,7 @@
         <v>44900</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22815,7 +22815,7 @@
         <v>45485</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>46111</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22961,7 +22961,7 @@
         <v>46114</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23034,7 +23034,7 @@
         <v>45160</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23107,7 +23107,7 @@
         <v>46123</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23180,7 +23180,7 @@
         <v>45714</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>44973</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23326,7 +23326,7 @@
         <v>44973</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23399,7 +23399,7 @@
         <v>45744</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>44907</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>46014</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>45758</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>46131</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
         <v>45334</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23842,7 +23842,7 @@
         <v>45526</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23915,7 +23915,7 @@
         <v>45684</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>45029</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24061,7 +24061,7 @@
         <v>45469</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24139,7 +24139,7 @@
         <v>44902</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>45265</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>46251</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         <v>44994</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>45707</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24504,7 +24504,7 @@
         <v>45608</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24577,7 +24577,7 @@
         <v>44866</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24650,7 +24650,7 @@
         <v>44720</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24723,7 +24723,7 @@
         <v>46251</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24796,7 +24796,7 @@
         <v>45205</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>45181</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>44630</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>45329</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>45329</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25161,7 +25161,7 @@
         <v>45120</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25234,7 +25234,7 @@
         <v>45645</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25307,7 +25307,7 @@
         <v>45096</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>45594</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>46254</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25526,7 +25526,7 @@
         <v>45630</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>45258</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>45041</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25745,7 +25745,7 @@
         <v>45187</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>45495</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>45495</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>46099</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>45226</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>45090</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26183,7 +26183,7 @@
         <v>44881</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26256,7 +26256,7 @@
         <v>46266</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>45183</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>45265</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26480,7 +26480,7 @@
         <v>45265</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>44531</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>46267</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26704,7 +26704,7 @@
         <v>45752</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26777,7 +26777,7 @@
         <v>44664</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26850,7 +26850,7 @@
         <v>45547</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>46273</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>45779</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>45608</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>45473</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>44911</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27298,7 +27298,7 @@
         <v>46279</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27371,7 +27371,7 @@
         <v>46279</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27444,7 +27444,7 @@
         <v>45530</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27517,7 +27517,7 @@
         <v>44911</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>45531</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         <v>45740</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>45711</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>45519</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>45790</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>45680</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>45728</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>46129</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28179,7 +28179,7 @@
         <v>45170</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28252,7 +28252,7 @@
         <v>45350</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>44997</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28398,7 +28398,7 @@
         <v>45818</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28471,7 +28471,7 @@
         <v>45786</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28544,7 +28544,7 @@
         <v>45821</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28617,7 +28617,7 @@
         <v>45096</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28690,7 +28690,7 @@
         <v>45784</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28763,7 +28763,7 @@
         <v>45838</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>45838</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>45841</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -28982,7 +28982,7 @@
         <v>45779</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29055,7 +29055,7 @@
         <v>45669</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29128,7 +29128,7 @@
         <v>45258</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29201,7 +29201,7 @@
         <v>45846</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29274,7 +29274,7 @@
         <v>45740</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29347,7 +29347,7 @@
         <v>45821</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29420,7 +29420,7 @@
         <v>45460</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29493,7 +29493,7 @@
         <v>45855</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29566,7 +29566,7 @@
         <v>45473</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>45861</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29717,7 +29717,7 @@
         <v>45882</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29795,7 +29795,7 @@
         <v>44257</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29868,7 +29868,7 @@
         <v>44607</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29946,7 +29946,7 @@
         <v>44607</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>45930</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>

--- a/Översikt TIDAHOLM.xlsx
+++ b/Översikt TIDAHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45534</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>44637</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>44902</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>46262</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>43986</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44607</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>44930</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>45183</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>46279</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44607</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>44512</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>44512</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>44865</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>45322</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>45899</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>46055</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>45925</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45930</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>45246</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45232</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>46289</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>44637</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>45684</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44607</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>44607</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>44607</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>46064</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>44519</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>44481</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>44573</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>44529</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>44550</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>44832</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>44630</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>44594</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>44615</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44508</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>44694</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>44512</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>44587</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>44889</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>44783</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>44546</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>44573</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>44703</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>44613</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>44869</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>44526</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>44474</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>44615</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>44623</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>44686</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>44615</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>44615</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>44522</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>44589</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>44615</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>44588</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44511</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>44550</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>44550</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>44550</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>44860</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         <v>44817</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>44812</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>44580</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>45329</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>45329</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>45098</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44866</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>45335</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>45204</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>45359</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44860</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>45265</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>44900</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>45530</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>44945</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>45474</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>45576</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>44973</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>46013</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>44958</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>46021</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>45728</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>45334</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>45485</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>45469</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>44529</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>45811</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>45672</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>45420</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         <v>45891</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>45099</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         <v>45240</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>45483</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>46042</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>46044</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>44911</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>46043</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>45897</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44630</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>45539</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>45899</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>45904</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>45904</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>45904</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>45904</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>45904</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>45587</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>45556</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>46051</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>46059</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>45007</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>44910</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>45919</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>45041</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>44900</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>45687</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>45930</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>45232</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>45146</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>45930</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>46079</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>45930</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>45930</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>45930</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>45547</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>46080</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>46080</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>45931</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>46084</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>46084</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11848,7 +11848,7 @@
         <v>45350</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>45170</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>44973</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>44973</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>45212</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         <v>46084</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>44630</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>44930</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>45594</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>45937</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>45548</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>44997</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>45048</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>45226</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>45684</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>46105</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>45707</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>45596</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         <v>45280</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>45352</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>46111</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>45603</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>45603</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>45581</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>45477</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>46114</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>45013</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>45580</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>45643</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>46123</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>44994</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         <v>45965</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>45967</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>45967</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>45967</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
         <v>45967</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>45967</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>45967</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14657,7 +14657,7 @@
         <v>45968</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>45967</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14813,7 +14813,7 @@
         <v>45967</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>44973</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>45000</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>45469</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>45414</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         <v>45096</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>46131</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>45979</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>45594</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>45981</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>45985</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>45608</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>45875</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>45630</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>44622</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15928,7 +15928,7 @@
         <v>45951</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         <v>45847</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>45919</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16147,7 +16147,7 @@
         <v>45534</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>45181</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         <v>44783</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>45709</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>46006</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>45818</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>45526</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>45784</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>44817</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16819,7 +16819,7 @@
         <v>45443</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16892,7 +16892,7 @@
         <v>44580</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         <v>45790</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>45911</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>45821</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>45779</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>45744</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>45786</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>44531</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         <v>44559</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17554,7 +17554,7 @@
         <v>45070</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>44865</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>44900</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         <v>45029</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>45096</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>45167</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>46153</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>46153</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18143,7 +18143,7 @@
         <v>44903</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18216,7 +18216,7 @@
         <v>45784</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18289,7 +18289,7 @@
         <v>45838</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18362,7 +18362,7 @@
         <v>45838</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         <v>45495</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18508,7 +18508,7 @@
         <v>45495</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>45392</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>45362</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18727,7 +18727,7 @@
         <v>45814</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18800,7 +18800,7 @@
         <v>45103</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
         <v>45103</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>45841</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>45846</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>45258</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>45821</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>45669</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>45779</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>45740</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19467,7 +19467,7 @@
         <v>44915</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19545,7 +19545,7 @@
         <v>45911</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>45460</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19691,7 +19691,7 @@
         <v>45855</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>45266</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19837,7 +19837,7 @@
         <v>45473</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>44831</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19983,7 +19983,7 @@
         <v>45628</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>45861</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>45006</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>46175</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>45576</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>46175</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>46175</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>45469</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>45373</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20650,7 +20650,7 @@
         <v>45608</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>44546</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>45105</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>46181</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20942,7 +20942,7 @@
         <v>46181</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>44476</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>46178</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21166,7 +21166,7 @@
         <v>45120</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21239,7 +21239,7 @@
         <v>45096</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>45443</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>45469</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
         <v>45469</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>45155</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>45047</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21692,7 +21692,7 @@
         <v>46191</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
         <v>45758</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>45669</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21916,7 +21916,7 @@
         <v>46181</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>44817</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>45630</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22135,7 +22135,7 @@
         <v>45882</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22213,7 +22213,7 @@
         <v>45721</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22286,7 +22286,7 @@
         <v>45267</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22359,7 +22359,7 @@
         <v>45030</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>45204</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         <v>45884</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>45594</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>46014</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22734,7 +22734,7 @@
         <v>45356</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>46251</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22880,7 +22880,7 @@
         <v>45205</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>45232</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>44610</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23104,7 +23104,7 @@
         <v>46251</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23177,7 +23177,7 @@
         <v>45623</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23250,7 +23250,7 @@
         <v>45187</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23323,7 +23323,7 @@
         <v>46254</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23396,7 +23396,7 @@
         <v>45090</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23469,7 +23469,7 @@
         <v>45637</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>45232</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23615,7 +23615,7 @@
         <v>45147</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23688,7 +23688,7 @@
         <v>44693</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>44636</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23834,7 +23834,7 @@
         <v>45758</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>45358</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23980,7 +23980,7 @@
         <v>45257</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>45215</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>44720</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
         <v>44685</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24272,7 +24272,7 @@
         <v>45752</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24345,7 +24345,7 @@
         <v>44720</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24418,7 +24418,7 @@
         <v>45714</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24491,7 +24491,7 @@
         <v>45265</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24564,7 +24564,7 @@
         <v>45265</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>44881</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
         <v>46266</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>46099</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>45314</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24929,7 +24929,7 @@
         <v>44973</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>46267</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25075,7 +25075,7 @@
         <v>45336</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>44806</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>45311</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25294,7 +25294,7 @@
         <v>45238</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>46273</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25440,7 +25440,7 @@
         <v>44911</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>44911</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25596,7 +25596,7 @@
         <v>45282</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25669,7 +25669,7 @@
         <v>46279</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25742,7 +25742,7 @@
         <v>45160</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>44985</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>44907</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25961,7 +25961,7 @@
         <v>45469</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26039,7 +26039,7 @@
         <v>44552</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26112,7 +26112,7 @@
         <v>44501</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26185,7 +26185,7 @@
         <v>44664</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         <v>45665</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26331,7 +26331,7 @@
         <v>45016</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26404,7 +26404,7 @@
         <v>46288</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>45099</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26555,7 +26555,7 @@
         <v>44719</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26628,7 +26628,7 @@
         <v>46129</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>46288</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         <v>45258</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26847,7 +26847,7 @@
         <v>44915</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>46064</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
         <v>46289</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>46279</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>46290</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27222,7 +27222,7 @@
         <v>46290</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>46290</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>46289</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>46290</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>45462</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>44902</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         <v>45068</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>45425</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>44900</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>45120</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27957,7 +27957,7 @@
         <v>45530</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28030,7 +28030,7 @@
         <v>45183</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28108,7 +28108,7 @@
         <v>45121</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28186,7 +28186,7 @@
         <v>45183</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>45469</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28342,7 +28342,7 @@
         <v>45225</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>44766</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28488,7 +28488,7 @@
         <v>45469</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28566,7 +28566,7 @@
         <v>45404</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
         <v>45103</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>45156</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>45481</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28863,7 +28863,7 @@
         <v>45105</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>44900</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>44972</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>45576</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>45580</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>45041</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>45358</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>45645</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29457,7 +29457,7 @@
         <v>45637</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>45779</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29603,7 +29603,7 @@
         <v>45608</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>45473</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29749,7 +29749,7 @@
         <v>45530</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>45790</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29895,7 +29895,7 @@
         <v>45519</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>45531</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>45740</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>45711</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>45680</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>44257</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44607</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>44607</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>45930</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>

--- a/Översikt TIDAHOLM.xlsx
+++ b/Översikt TIDAHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45534</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>44637</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>44902</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>46262</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>43986</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44607</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>44930</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>45183</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>46279</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44607</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>44512</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>44512</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>44865</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>45322</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>45899</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>46055</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>45925</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>45930</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>45246</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45232</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>46289</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>44637</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>45684</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44607</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>44607</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>44607</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>46064</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>44519</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>44481</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>44573</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>44529</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>44550</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>44832</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>44630</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>44594</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>44615</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44508</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>44694</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>44512</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>44587</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>44889</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>44783</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>44546</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>44573</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>44703</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>44613</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>44869</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>44526</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>44474</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>44615</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>44623</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>44686</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>44615</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>44615</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>44522</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>44589</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>44615</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>44588</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44511</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>44550</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>44550</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>44550</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>44860</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         <v>44817</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>44812</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>44580</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>45329</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>45329</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>45098</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44866</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>45335</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>45204</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>45359</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44860</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>45265</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>44900</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>45530</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>44945</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>45474</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         <v>45576</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>44973</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7962,7 +7962,7 @@
         <v>46013</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8035,7 +8035,7 @@
         <v>44958</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>46021</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>45728</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>45334</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>45485</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>45469</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>44529</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>45811</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>45672</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>45420</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         <v>45891</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>45099</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         <v>45240</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>45483</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>46042</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>46044</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>44911</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9296,7 +9296,7 @@
         <v>46043</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>45897</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9442,7 +9442,7 @@
         <v>44630</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>45539</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>45899</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>45904</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>45904</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9817,7 +9817,7 @@
         <v>45904</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         <v>45904</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>45904</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>45587</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10124,7 +10124,7 @@
         <v>45556</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>46051</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10275,7 +10275,7 @@
         <v>46059</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>45007</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10421,7 +10421,7 @@
         <v>44910</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>45919</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>45041</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>44900</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>45687</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>45930</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>45232</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>45146</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>45930</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11098,7 +11098,7 @@
         <v>46079</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>45930</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>45930</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>45930</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11405,7 +11405,7 @@
         <v>45547</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11483,7 +11483,7 @@
         <v>46080</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>46080</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>45931</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>46084</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11775,7 +11775,7 @@
         <v>46084</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11848,7 +11848,7 @@
         <v>45350</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>45170</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>44973</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>44973</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>45212</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         <v>46084</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>44630</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12359,7 +12359,7 @@
         <v>44930</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12432,7 +12432,7 @@
         <v>45594</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>45937</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>45548</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>44997</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>45048</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12797,7 +12797,7 @@
         <v>45226</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         <v>45684</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>46105</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>45707</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>45596</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         <v>45280</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>45352</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>46111</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>45603</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>45603</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>45581</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>45477</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>46114</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>45013</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>45580</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>45643</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>46123</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14038,7 +14038,7 @@
         <v>44994</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14111,7 +14111,7 @@
         <v>45965</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>45967</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>45967</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>45967</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
         <v>45967</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>45967</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>45967</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14657,7 +14657,7 @@
         <v>45968</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>45967</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14813,7 +14813,7 @@
         <v>45967</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>44973</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14964,7 +14964,7 @@
         <v>45000</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>45469</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>45414</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         <v>45096</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>46131</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>45979</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>45594</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>45981</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>45985</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>45608</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>45875</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>45630</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>44622</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15928,7 +15928,7 @@
         <v>45951</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         <v>45847</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>45919</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16147,7 +16147,7 @@
         <v>45534</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>45181</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16298,7 +16298,7 @@
         <v>44783</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>45709</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>46006</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>45818</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>45526</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>45784</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>44817</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16819,7 +16819,7 @@
         <v>45443</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16892,7 +16892,7 @@
         <v>44580</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         <v>45790</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>45911</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>45821</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>45779</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>45744</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17330,7 +17330,7 @@
         <v>45786</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17403,7 +17403,7 @@
         <v>44531</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         <v>44559</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17554,7 +17554,7 @@
         <v>45070</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>44865</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>44900</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17778,7 +17778,7 @@
         <v>45029</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>45096</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17924,7 +17924,7 @@
         <v>45167</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>46153</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>46153</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18143,7 +18143,7 @@
         <v>44903</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18216,7 +18216,7 @@
         <v>45784</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18289,7 +18289,7 @@
         <v>45838</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18362,7 +18362,7 @@
         <v>45838</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         <v>45495</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18508,7 +18508,7 @@
         <v>45495</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>45392</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18654,7 +18654,7 @@
         <v>45362</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18727,7 +18727,7 @@
         <v>45814</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18800,7 +18800,7 @@
         <v>45103</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18878,7 +18878,7 @@
         <v>45103</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18956,7 +18956,7 @@
         <v>45841</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19029,7 +19029,7 @@
         <v>45846</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19102,7 +19102,7 @@
         <v>45258</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19175,7 +19175,7 @@
         <v>45821</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19248,7 +19248,7 @@
         <v>45669</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>45779</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>45740</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19467,7 +19467,7 @@
         <v>44915</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19545,7 +19545,7 @@
         <v>45911</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19618,7 +19618,7 @@
         <v>45460</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19691,7 +19691,7 @@
         <v>45855</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19764,7 +19764,7 @@
         <v>45266</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19837,7 +19837,7 @@
         <v>45473</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>44831</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19983,7 +19983,7 @@
         <v>45628</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>45861</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>45006</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>46175</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>45576</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>46175</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>46175</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>45469</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>45373</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20650,7 +20650,7 @@
         <v>45608</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>44546</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>45105</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>46181</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20942,7 +20942,7 @@
         <v>46181</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>44476</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>46178</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21166,7 +21166,7 @@
         <v>45120</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21239,7 +21239,7 @@
         <v>45096</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>45443</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>45469</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
         <v>45469</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21541,7 +21541,7 @@
         <v>45155</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>45047</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21692,7 +21692,7 @@
         <v>46191</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
         <v>45758</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>45669</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21916,7 +21916,7 @@
         <v>46181</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21989,7 +21989,7 @@
         <v>44817</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>45630</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22135,7 +22135,7 @@
         <v>45882</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22213,7 +22213,7 @@
         <v>45721</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22286,7 +22286,7 @@
         <v>45267</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22359,7 +22359,7 @@
         <v>45030</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>45204</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         <v>45884</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>45594</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>46014</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22734,7 +22734,7 @@
         <v>45356</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>46251</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22880,7 +22880,7 @@
         <v>45205</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>45232</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>44610</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23104,7 +23104,7 @@
         <v>46251</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23177,7 +23177,7 @@
         <v>45623</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23250,7 +23250,7 @@
         <v>45187</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23323,7 +23323,7 @@
         <v>46254</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23396,7 +23396,7 @@
         <v>45090</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23469,7 +23469,7 @@
         <v>45637</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>45232</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23615,7 +23615,7 @@
         <v>45147</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23688,7 +23688,7 @@
         <v>44693</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>44636</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23834,7 +23834,7 @@
         <v>45758</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>45358</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23980,7 +23980,7 @@
         <v>45257</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>45215</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>44720</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
         <v>44685</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24272,7 +24272,7 @@
         <v>45752</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24345,7 +24345,7 @@
         <v>44720</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24418,7 +24418,7 @@
         <v>45714</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24491,7 +24491,7 @@
         <v>45265</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24564,7 +24564,7 @@
         <v>45265</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>44881</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24710,7 +24710,7 @@
         <v>46266</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24783,7 +24783,7 @@
         <v>46099</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24856,7 +24856,7 @@
         <v>45314</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24929,7 +24929,7 @@
         <v>44973</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>46267</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25075,7 +25075,7 @@
         <v>45336</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>44806</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25221,7 +25221,7 @@
         <v>45311</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25294,7 +25294,7 @@
         <v>45238</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>46273</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25440,7 +25440,7 @@
         <v>44911</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>44911</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25596,7 +25596,7 @@
         <v>45282</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25669,7 +25669,7 @@
         <v>46279</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25742,7 +25742,7 @@
         <v>45160</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>44985</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>44907</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25961,7 +25961,7 @@
         <v>45469</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26039,7 +26039,7 @@
         <v>44552</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26112,7 +26112,7 @@
         <v>44501</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26185,7 +26185,7 @@
         <v>44664</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         <v>45665</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26331,7 +26331,7 @@
         <v>45016</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26404,7 +26404,7 @@
         <v>46288</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26477,7 +26477,7 @@
         <v>45099</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26555,7 +26555,7 @@
         <v>44719</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26628,7 +26628,7 @@
         <v>46129</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>46288</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26774,7 +26774,7 @@
         <v>45258</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26847,7 +26847,7 @@
         <v>44915</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>46064</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27003,7 +27003,7 @@
         <v>46289</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27076,7 +27076,7 @@
         <v>46279</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27149,7 +27149,7 @@
         <v>46290</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27222,7 +27222,7 @@
         <v>46290</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27295,7 +27295,7 @@
         <v>46290</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>46289</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27441,7 +27441,7 @@
         <v>46290</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27514,7 +27514,7 @@
         <v>45462</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>44902</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         <v>45068</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>45425</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27806,7 +27806,7 @@
         <v>44900</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>45120</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27957,7 +27957,7 @@
         <v>45530</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28030,7 +28030,7 @@
         <v>45183</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28108,7 +28108,7 @@
         <v>45121</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28186,7 +28186,7 @@
         <v>45183</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>45469</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28342,7 +28342,7 @@
         <v>45225</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>44766</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28488,7 +28488,7 @@
         <v>45469</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28566,7 +28566,7 @@
         <v>45404</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
         <v>45103</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>45156</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>45481</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28863,7 +28863,7 @@
         <v>45105</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>44900</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>44972</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>45576</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>45580</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>45041</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>45358</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>45645</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29457,7 +29457,7 @@
         <v>45637</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29530,7 +29530,7 @@
         <v>45779</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29603,7 +29603,7 @@
         <v>45608</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>45473</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29749,7 +29749,7 @@
         <v>45530</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>45790</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29895,7 +29895,7 @@
         <v>45519</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29968,7 +29968,7 @@
         <v>45531</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>45740</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>45711</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>45680</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>44257</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44607</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>44607</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>45930</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>

--- a/Översikt TIDAHOLM.xlsx
+++ b/Översikt TIDAHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45534</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>44637</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>44902</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>46262</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>43986</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44607</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>45183</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>44930</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>46279</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44607</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>44512</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>44512</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>44865</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>45246</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>45899</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>45925</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>46055</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>45930</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>45232</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>46289</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>45684</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>44637</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>45322</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44607</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>44607</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>44607</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>46064</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>44519</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>44573</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>44481</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>44529</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>44550</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>44832</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>44594</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>44630</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>44615</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44508</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>44694</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>44512</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>44587</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>44889</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>44783</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>44546</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>44573</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>44703</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>44613</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>44869</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>44526</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>44474</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>44615</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>44623</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>44686</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>44615</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>44615</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>44522</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>44589</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>44615</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>44588</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44511</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>44550</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>44550</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>44550</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>44812</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         <v>44817</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>44860</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>44580</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>44719</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>45758</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>45534</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>45266</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>45267</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>45425</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>44693</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44900</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>44903</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>45483</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>44817</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>45103</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>45099</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         <v>45099</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>44559</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>45721</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>45643</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>45580</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>44610</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>45120</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>45530</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>45041</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>45016</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>45167</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>46006</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>45531</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>45740</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>45481</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         <v>45884</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>46013</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>44860</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>45711</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>45519</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>45790</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>45811</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>46021</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>45891</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>45420</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>45314</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>45897</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>45899</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>45680</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>45103</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>45335</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>45904</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>45904</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10255,7 +10255,7 @@
         <v>45904</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>45904</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>45904</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>45240</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>45232</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>46043</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>45728</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>46042</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>44476</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>46044</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>45687</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11083,7 +11083,7 @@
         <v>45919</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>44636</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>45170</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>46051</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>45930</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>45930</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>46059</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>45930</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>45930</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         <v>45930</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>45931</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>45146</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>45637</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>45937</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>45068</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>45350</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>44997</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>45204</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>46080</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>46079</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>46080</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>46084</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>45443</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>46084</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>46084</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>45637</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13011,7 +13011,7 @@
         <v>45965</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>44831</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         <v>45967</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>45967</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13318,7 +13318,7 @@
         <v>45967</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>45623</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>45967</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>45967</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>45967</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>45967</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
         <v>44720</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13854,7 +13854,7 @@
         <v>45967</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>45968</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>45215</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         <v>45212</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14156,7 +14156,7 @@
         <v>45359</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>45548</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>45183</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>45818</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>45105</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>46105</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>45979</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>45280</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>45336</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>45356</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>45981</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>45581</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>45985</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15125,7 +15125,7 @@
         <v>46111</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15198,7 +15198,7 @@
         <v>45786</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>46114</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15344,7 +15344,7 @@
         <v>45103</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         <v>45821</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>44945</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>45556</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>46123</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>44817</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>45669</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>45951</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15933,7 +15933,7 @@
         <v>45096</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>44783</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16084,7 +16084,7 @@
         <v>46131</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>45784</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>45232</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>45526</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>45098</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16454,7 +16454,7 @@
         <v>45838</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>45462</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>45838</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>45006</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>45630</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16819,7 +16819,7 @@
         <v>44900</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>45608</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16970,7 +16970,7 @@
         <v>45841</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         <v>45779</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>45669</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>45258</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>45784</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>45846</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17408,7 +17408,7 @@
         <v>45740</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         <v>45821</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17554,7 +17554,7 @@
         <v>45460</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>45875</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>45665</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>45855</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>45919</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>45477</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>45911</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18065,7 +18065,7 @@
         <v>45576</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18138,7 +18138,7 @@
         <v>45779</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>45282</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>45790</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>45474</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         <v>45473</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18508,7 +18508,7 @@
         <v>44622</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>45861</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>45121</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>45580</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>44900</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>45709</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>45847</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>45358</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>45358</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>45576</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>45156</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>45539</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>44973</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>44580</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19545,7 +19545,7 @@
         <v>45232</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>45105</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>46153</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>46153</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>45030</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>45469</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>45469</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>45469</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20149,7 +20149,7 @@
         <v>44529</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>45362</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20295,7 +20295,7 @@
         <v>44973</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>44806</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>45596</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20514,7 +20514,7 @@
         <v>45352</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>45814</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>45392</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>45603</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>45603</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>45530</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20952,7 +20952,7 @@
         <v>45443</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21025,7 +21025,7 @@
         <v>45911</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21098,7 +21098,7 @@
         <v>44630</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>45530</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>45628</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21317,7 +21317,7 @@
         <v>44910</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>45594</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
         <v>46175</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>46175</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>45882</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>46175</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>45672</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>45096</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>45469</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>46178</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>46181</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22135,7 +22135,7 @@
         <v>46181</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>45414</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>44552</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>45469</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>44546</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         <v>46191</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>46181</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>45404</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>45048</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>45000</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>45013</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>44685</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>45047</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>46014</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23172,7 +23172,7 @@
         <v>45204</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23245,7 +23245,7 @@
         <v>45469</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23323,7 +23323,7 @@
         <v>45469</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23401,7 +23401,7 @@
         <v>45311</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23474,7 +23474,7 @@
         <v>44958</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>45147</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23620,7 +23620,7 @@
         <v>45576</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>44930</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>44973</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>44915</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23922,7 +23922,7 @@
         <v>44915</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24000,7 +24000,7 @@
         <v>44911</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>46099</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24151,7 +24151,7 @@
         <v>44881</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>44501</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>46266</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>44972</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>46267</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>46273</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24589,7 +24589,7 @@
         <v>44766</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24662,7 +24662,7 @@
         <v>45594</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24735,7 +24735,7 @@
         <v>45238</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24808,7 +24808,7 @@
         <v>45373</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24881,7 +24881,7 @@
         <v>44911</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24959,7 +24959,7 @@
         <v>46279</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25032,7 +25032,7 @@
         <v>44865</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25105,7 +25105,7 @@
         <v>44911</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>45070</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>45155</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25334,7 +25334,7 @@
         <v>44900</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>45225</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>45587</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25558,7 +25558,7 @@
         <v>45007</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25631,7 +25631,7 @@
         <v>44985</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>45257</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25777,7 +25777,7 @@
         <v>46129</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25850,7 +25850,7 @@
         <v>44900</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>45485</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>46289</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>46289</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>46279</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>46288</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>45160</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>46288</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>45714</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26512,7 +26512,7 @@
         <v>46290</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>44973</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26658,7 +26658,7 @@
         <v>44973</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>45744</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         <v>44907</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>46290</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>45758</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         <v>46290</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>46064</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         <v>46290</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>45334</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>45684</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>45029</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27466,7 +27466,7 @@
         <v>45469</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         <v>46251</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27617,7 +27617,7 @@
         <v>46251</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27690,7 +27690,7 @@
         <v>44902</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27763,7 +27763,7 @@
         <v>45265</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>44994</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>45707</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>45608</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>44866</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         <v>46254</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>44720</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>45205</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28347,7 +28347,7 @@
         <v>45181</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28420,7 +28420,7 @@
         <v>44630</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28493,7 +28493,7 @@
         <v>45329</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28566,7 +28566,7 @@
         <v>45329</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
         <v>45120</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28712,7 +28712,7 @@
         <v>45645</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         <v>45096</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>45594</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>45630</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>45258</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
         <v>45041</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
         <v>45187</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>45495</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29296,7 +29296,7 @@
         <v>45495</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         <v>45226</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>45090</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>45183</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>45265</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>45265</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>44531</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>45752</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>44664</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>45547</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>45779</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>45608</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>45473</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>44257</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44607</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>44607</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>45930</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>

--- a/Översikt TIDAHOLM.xlsx
+++ b/Översikt TIDAHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45534</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>44637</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>44902</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>46262</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>43986</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44607</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>45183</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>44930</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>46279</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44607</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>44512</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>44512</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>44865</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>45246</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>45899</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>45925</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>46055</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>45930</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>45232</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>46289</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>45684</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         <v>44637</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>45322</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44607</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>44607</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>44607</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>46064</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>44519</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>44573</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>44481</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>44529</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>44550</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>44832</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>44594</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>44630</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>44615</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44508</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>44694</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>44512</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>44587</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>44889</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>44783</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>44546</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>44573</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>44703</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>44613</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>44869</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>44526</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>44474</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5601,7 +5601,7 @@
         <v>44615</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>44623</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>44686</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>44615</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>44615</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>44522</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>44589</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>44615</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>44588</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44511</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>44550</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>44550</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>44550</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>44812</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         <v>44817</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>44860</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>44580</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>44719</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>45758</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6993,7 +6993,7 @@
         <v>45534</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>45266</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>45267</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>45425</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>44693</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44900</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>44903</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>45483</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>44817</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>45103</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>45099</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         <v>45099</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>44559</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>45721</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>45643</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>45580</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>44610</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>45120</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>45530</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>45041</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>45016</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>45167</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>46006</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>45531</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>45740</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>45481</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         <v>45884</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>46013</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>44860</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>45711</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>45519</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>45790</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>45811</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>46021</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>45891</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>45420</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>45314</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>45897</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>45899</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>45680</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>45103</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>45335</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>45904</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>45904</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10255,7 +10255,7 @@
         <v>45904</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10333,7 +10333,7 @@
         <v>45904</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10411,7 +10411,7 @@
         <v>45904</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>45240</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>45232</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>46043</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>45728</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>46042</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>44476</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>46044</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>45687</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11083,7 +11083,7 @@
         <v>45919</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11156,7 +11156,7 @@
         <v>44636</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>45170</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11302,7 +11302,7 @@
         <v>46051</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>45930</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>45930</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>46059</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>45930</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>45930</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         <v>45930</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>45931</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11916,7 +11916,7 @@
         <v>45146</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>45637</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>45937</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>45068</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>45350</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>44997</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>45204</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>46080</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>46079</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12573,7 +12573,7 @@
         <v>46080</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>46084</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12719,7 +12719,7 @@
         <v>45443</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>46084</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>46084</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12938,7 +12938,7 @@
         <v>45637</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13011,7 +13011,7 @@
         <v>45965</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13089,7 +13089,7 @@
         <v>44831</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13162,7 +13162,7 @@
         <v>45967</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>45967</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13318,7 +13318,7 @@
         <v>45967</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>45623</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>45967</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13547,7 +13547,7 @@
         <v>45967</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>45967</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>45967</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
         <v>44720</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13854,7 +13854,7 @@
         <v>45967</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>45968</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>45215</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14083,7 +14083,7 @@
         <v>45212</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14156,7 +14156,7 @@
         <v>45359</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14229,7 +14229,7 @@
         <v>45548</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14302,7 +14302,7 @@
         <v>45183</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>45818</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>45105</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>46105</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>45979</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>45280</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>45336</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>45356</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>45981</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>45581</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15052,7 +15052,7 @@
         <v>45985</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15125,7 +15125,7 @@
         <v>46111</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15198,7 +15198,7 @@
         <v>45786</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>46114</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15344,7 +15344,7 @@
         <v>45103</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         <v>45821</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>44945</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>45556</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>46123</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15714,7 +15714,7 @@
         <v>44817</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>45669</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15860,7 +15860,7 @@
         <v>45951</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15933,7 +15933,7 @@
         <v>45096</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16006,7 +16006,7 @@
         <v>44783</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16084,7 +16084,7 @@
         <v>46131</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16157,7 +16157,7 @@
         <v>45784</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16230,7 +16230,7 @@
         <v>45232</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16303,7 +16303,7 @@
         <v>45526</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16376,7 +16376,7 @@
         <v>45098</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16454,7 +16454,7 @@
         <v>45838</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>45462</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16600,7 +16600,7 @@
         <v>45838</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>45006</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>45630</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16819,7 +16819,7 @@
         <v>44900</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16897,7 +16897,7 @@
         <v>45608</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16970,7 +16970,7 @@
         <v>45841</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         <v>45779</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>45669</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>45258</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>45784</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>45846</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17408,7 +17408,7 @@
         <v>45740</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17481,7 +17481,7 @@
         <v>45821</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17554,7 +17554,7 @@
         <v>45460</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>45875</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>45665</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>45855</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>45919</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>45477</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>45911</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18065,7 +18065,7 @@
         <v>45576</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18138,7 +18138,7 @@
         <v>45779</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18211,7 +18211,7 @@
         <v>45282</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>45790</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>45474</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         <v>45473</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18508,7 +18508,7 @@
         <v>44622</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>45861</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>45121</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18737,7 +18737,7 @@
         <v>45580</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>44900</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>45709</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>45847</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>45358</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>45358</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>45576</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>45156</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>45539</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>44973</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>44580</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19545,7 +19545,7 @@
         <v>45232</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19623,7 +19623,7 @@
         <v>45105</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>46153</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19769,7 +19769,7 @@
         <v>46153</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19842,7 +19842,7 @@
         <v>45030</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>45469</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19993,7 +19993,7 @@
         <v>45469</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>45469</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20149,7 +20149,7 @@
         <v>44529</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20222,7 +20222,7 @@
         <v>45362</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20295,7 +20295,7 @@
         <v>44973</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         <v>44806</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>45596</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20514,7 +20514,7 @@
         <v>45352</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>45814</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>45392</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>45603</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>45603</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>45530</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20952,7 +20952,7 @@
         <v>45443</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21025,7 +21025,7 @@
         <v>45911</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21098,7 +21098,7 @@
         <v>44630</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21171,7 +21171,7 @@
         <v>45530</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>45628</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21317,7 +21317,7 @@
         <v>44910</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>45594</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21463,7 +21463,7 @@
         <v>46175</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>46175</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>45882</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>46175</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21760,7 +21760,7 @@
         <v>45672</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21833,7 +21833,7 @@
         <v>45096</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>45469</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>46178</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22062,7 +22062,7 @@
         <v>46181</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22135,7 +22135,7 @@
         <v>46181</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>45414</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>44552</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>45469</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>44546</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         <v>46191</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22583,7 +22583,7 @@
         <v>46181</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>45404</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22729,7 +22729,7 @@
         <v>45048</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22802,7 +22802,7 @@
         <v>45000</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22875,7 +22875,7 @@
         <v>45013</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22948,7 +22948,7 @@
         <v>44685</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23021,7 +23021,7 @@
         <v>45047</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23094,7 +23094,7 @@
         <v>46014</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23172,7 +23172,7 @@
         <v>45204</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23245,7 +23245,7 @@
         <v>45469</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23323,7 +23323,7 @@
         <v>45469</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23401,7 +23401,7 @@
         <v>45311</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23474,7 +23474,7 @@
         <v>44958</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>45147</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23620,7 +23620,7 @@
         <v>45576</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>44930</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>44973</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>44915</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23922,7 +23922,7 @@
         <v>44915</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24000,7 +24000,7 @@
         <v>44911</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>46099</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24151,7 +24151,7 @@
         <v>44881</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>44501</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         <v>46266</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24370,7 +24370,7 @@
         <v>44972</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>46267</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24516,7 +24516,7 @@
         <v>46273</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24589,7 +24589,7 @@
         <v>44766</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24662,7 +24662,7 @@
         <v>45594</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24735,7 +24735,7 @@
         <v>45238</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24808,7 +24808,7 @@
         <v>45373</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24881,7 +24881,7 @@
         <v>44911</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24959,7 +24959,7 @@
         <v>46279</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25032,7 +25032,7 @@
         <v>44865</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25105,7 +25105,7 @@
         <v>44911</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25183,7 +25183,7 @@
         <v>45070</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25256,7 +25256,7 @@
         <v>45155</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25334,7 +25334,7 @@
         <v>44900</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>45225</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>45587</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25558,7 +25558,7 @@
         <v>45007</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25631,7 +25631,7 @@
         <v>44985</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>45257</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25777,7 +25777,7 @@
         <v>46129</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25850,7 +25850,7 @@
         <v>44900</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>45485</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>46289</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26074,7 +26074,7 @@
         <v>46289</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>46279</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>46288</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>45160</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>46288</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>45714</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26512,7 +26512,7 @@
         <v>46290</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>44973</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26658,7 +26658,7 @@
         <v>44973</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>45744</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         <v>44907</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>46290</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26950,7 +26950,7 @@
         <v>45758</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27023,7 +27023,7 @@
         <v>46290</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>46064</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27174,7 +27174,7 @@
         <v>46290</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27247,7 +27247,7 @@
         <v>45334</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27320,7 +27320,7 @@
         <v>45684</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27393,7 +27393,7 @@
         <v>45029</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27466,7 +27466,7 @@
         <v>45469</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         <v>46251</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27617,7 +27617,7 @@
         <v>46251</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27690,7 +27690,7 @@
         <v>44902</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27763,7 +27763,7 @@
         <v>45265</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27836,7 +27836,7 @@
         <v>44994</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>45707</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>45608</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>44866</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         <v>46254</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>44720</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>45205</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28347,7 +28347,7 @@
         <v>45181</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28420,7 +28420,7 @@
         <v>44630</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28493,7 +28493,7 @@
         <v>45329</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28566,7 +28566,7 @@
         <v>45329</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
         <v>45120</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28712,7 +28712,7 @@
         <v>45645</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         <v>45096</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>45594</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>45630</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29004,7 +29004,7 @@
         <v>45258</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29077,7 +29077,7 @@
         <v>45041</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29150,7 +29150,7 @@
         <v>45187</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         <v>45495</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29296,7 +29296,7 @@
         <v>45495</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         <v>45226</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>45090</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29515,7 +29515,7 @@
         <v>45183</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>45265</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>45265</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>44531</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>45752</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>44664</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>45547</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>45779</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30114,7 +30114,7 @@
         <v>45608</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>45473</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>44257</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44607</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>44607</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>45930</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>

--- a/Översikt TIDAHOLM.xlsx
+++ b/Översikt TIDAHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45534</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>44637</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>44902</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>46262</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>43986</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44607</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>44930</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>45183</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>46279</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44607</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>44512</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>44512</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>44865</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>45322</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>44637</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>45899</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>45684</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>45925</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45246</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>45232</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>46055</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>46289</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44607</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>44607</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>44607</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>46064</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>44519</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>44481</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>44573</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>44529</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>44550</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>44832</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>44594</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>44615</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>44630</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44508</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>44694</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>44512</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>44587</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>44889</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>44783</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>44546</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>44615</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>44588</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>44623</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>44511</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>44573</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>44703</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>44589</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>44613</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>44869</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>44550</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>44550</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>44550</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>44686</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>44817</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>44615</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44615</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>44860</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>44812</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>44526</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>44615</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         <v>44522</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>44866</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>45070</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>45204</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>45121</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>44860</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44865</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>45183</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>44580</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>45469</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>45225</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>44900</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>44766</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>45469</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>45404</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>45029</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>45167</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>45265</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>44903</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>45329</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>45329</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>45495</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>45495</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>45362</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>45103</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         <v>45156</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>45103</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>45103</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>44900</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>45481</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         <v>45530</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>44945</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         <v>45359</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>45098</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>45335</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>44915</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>45884</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>45474</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>45105</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>44973</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>45576</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>44900</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>44958</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>45266</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>44831</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>44972</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>45576</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>45580</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>45811</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>45672</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>45006</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>45041</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>45334</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>45576</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>45485</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>45891</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>45897</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>45469</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>45358</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>44529</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>45645</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         <v>45899</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>45420</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>45904</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>45904</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>45099</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>45637</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>45904</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>45483</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>45904</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11848,7 +11848,7 @@
         <v>45904</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>44911</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>45373</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>45608</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>44546</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
         <v>44630</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         <v>45539</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>45105</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>45779</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>45120</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>45587</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>45608</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>45096</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         <v>45473</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>45443</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12953,7 +12953,7 @@
         <v>45530</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13026,7 +13026,7 @@
         <v>45556</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>45469</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>45469</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>45919</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>45155</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>45047</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         <v>45007</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         <v>44910</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>45758</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         <v>45790</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>45519</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13844,7 +13844,7 @@
         <v>45531</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>45669</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>45740</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14063,7 +14063,7 @@
         <v>45041</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>44817</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>44900</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>45711</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         <v>45930</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>45680</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>45930</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>45687</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14662,7 +14662,7 @@
         <v>45630</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>45232</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14813,7 +14813,7 @@
         <v>45930</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>45930</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>45146</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>45547</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>45728</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>44973</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>44973</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>45212</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>45931</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>44630</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>44930</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>45594</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>45721</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>45267</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
         <v>45548</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         <v>45030</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
         <v>45204</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45594</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>45356</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>45048</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>45226</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>45937</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
         <v>45205</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         <v>45350</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16580,7 +16580,7 @@
         <v>45170</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>45232</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>44610</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>45684</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>45707</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>45623</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>44997</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>45187</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>45596</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>45280</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>45352</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>45603</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         <v>45603</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>45581</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>45090</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>45637</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>45232</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>45818</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>45477</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17972,7 +17972,7 @@
         <v>45147</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>45013</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>45580</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
         <v>44693</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>45821</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         <v>45643</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18410,7 +18410,7 @@
         <v>45786</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>44994</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>44636</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>45758</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>45358</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18775,7 +18775,7 @@
         <v>45257</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>44973</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>45096</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>45215</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>44720</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>45784</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>45838</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>45838</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45000</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45469</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19510,7 +19510,7 @@
         <v>44685</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>45414</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>45096</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>45594</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19802,7 +19802,7 @@
         <v>45752</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>45965</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19953,7 +19953,7 @@
         <v>44720</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>45841</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>45967</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>45967</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>45967</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>45967</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>45967</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>45967</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20567,7 +20567,7 @@
         <v>45968</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20645,7 +20645,7 @@
         <v>45967</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>45967</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20801,7 +20801,7 @@
         <v>45714</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20874,7 +20874,7 @@
         <v>45608</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>45846</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>45630</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>45265</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21166,7 +21166,7 @@
         <v>45265</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21239,7 +21239,7 @@
         <v>45258</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>45821</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>45669</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>45779</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>45740</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21604,7 +21604,7 @@
         <v>45314</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21677,7 +21677,7 @@
         <v>45460</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21750,7 +21750,7 @@
         <v>44973</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21823,7 +21823,7 @@
         <v>45855</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21896,7 +21896,7 @@
         <v>45473</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>45336</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>45861</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22120,7 +22120,7 @@
         <v>45534</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>45181</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>44783</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         <v>45709</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
         <v>44806</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22495,7 +22495,7 @@
         <v>45311</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>45979</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22646,7 +22646,7 @@
         <v>45238</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22719,7 +22719,7 @@
         <v>44817</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22792,7 +22792,7 @@
         <v>45443</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
         <v>44580</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22938,7 +22938,7 @@
         <v>45282</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23011,7 +23011,7 @@
         <v>45882</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23089,7 +23089,7 @@
         <v>45981</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>45744</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>45160</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>46105</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23386,7 +23386,7 @@
         <v>45985</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>44985</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23532,7 +23532,7 @@
         <v>44531</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>44907</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>46111</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>45469</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23834,7 +23834,7 @@
         <v>44559</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>46114</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23980,7 +23980,7 @@
         <v>44552</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>44501</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>44664</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
         <v>45665</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24272,7 +24272,7 @@
         <v>46123</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24345,7 +24345,7 @@
         <v>45951</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24418,7 +24418,7 @@
         <v>45016</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24491,7 +24491,7 @@
         <v>45099</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24569,7 +24569,7 @@
         <v>44719</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24642,7 +24642,7 @@
         <v>46131</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>45258</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         <v>46006</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24866,7 +24866,7 @@
         <v>44915</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24944,7 +24944,7 @@
         <v>45875</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25017,7 +25017,7 @@
         <v>44622</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>46013</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>46021</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25236,7 +25236,7 @@
         <v>45462</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25309,7 +25309,7 @@
         <v>45847</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25382,7 +25382,7 @@
         <v>45919</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25455,7 +25455,7 @@
         <v>44902</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>45068</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>45425</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25674,7 +25674,7 @@
         <v>45240</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25752,7 +25752,7 @@
         <v>46042</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>45526</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25898,7 +25898,7 @@
         <v>45784</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>44900</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26049,7 +26049,7 @@
         <v>46044</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>45790</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26195,7 +26195,7 @@
         <v>46043</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26268,7 +26268,7 @@
         <v>45911</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26341,7 +26341,7 @@
         <v>45120</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26414,7 +26414,7 @@
         <v>45779</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26487,7 +26487,7 @@
         <v>45530</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26560,7 +26560,7 @@
         <v>45183</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>46051</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>46059</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>46153</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26862,7 +26862,7 @@
         <v>46153</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>46079</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>46080</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27081,7 +27081,7 @@
         <v>46080</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         <v>46084</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27227,7 +27227,7 @@
         <v>46084</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27300,7 +27300,7 @@
         <v>46084</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27373,7 +27373,7 @@
         <v>45392</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>45814</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27519,7 +27519,7 @@
         <v>45911</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27592,7 +27592,7 @@
         <v>45628</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27665,7 +27665,7 @@
         <v>46175</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>46175</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27811,7 +27811,7 @@
         <v>46175</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>45469</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27962,7 +27962,7 @@
         <v>46181</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>46181</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28108,7 +28108,7 @@
         <v>46178</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28186,7 +28186,7 @@
         <v>46191</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>46181</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28337,7 +28337,7 @@
         <v>46014</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>44881</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28488,7 +28488,7 @@
         <v>46266</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28561,7 +28561,7 @@
         <v>46099</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28634,7 +28634,7 @@
         <v>46267</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>46273</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28780,7 +28780,7 @@
         <v>44911</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>44911</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>46279</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29009,7 +29009,7 @@
         <v>46288</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
         <v>46129</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29155,7 +29155,7 @@
         <v>46288</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29228,7 +29228,7 @@
         <v>46064</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29306,7 +29306,7 @@
         <v>46289</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29379,7 +29379,7 @@
         <v>46279</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>46290</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>46290</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29598,7 +29598,7 @@
         <v>46290</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29671,7 +29671,7 @@
         <v>46289</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29744,7 +29744,7 @@
         <v>46290</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>46251</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>46251</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>46254</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30036,7 +30036,7 @@
         <v>46303</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30109,7 +30109,7 @@
         <v>44257</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30182,7 +30182,7 @@
         <v>44607</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>44607</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         <v>45930</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>

--- a/Översikt TIDAHOLM.xlsx
+++ b/Översikt TIDAHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45534</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>44637</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>44902</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>46262</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>43986</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44607</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>44930</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>45183</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>46279</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44607</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>44512</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>44512</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>44865</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>45322</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>44637</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>45899</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>45684</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>45925</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45930</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45246</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>45232</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>46055</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>46289</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44607</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>44607</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>44607</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>46064</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>44519</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>44481</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>44573</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>44529</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>44550</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>44832</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>44594</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>44615</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>44630</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44508</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>44694</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>44512</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>44587</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>44889</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5012,7 +5012,7 @@
         <v>44783</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>44546</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>44615</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>44588</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>44623</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>44511</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>44573</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>44703</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>44589</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>44613</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>44869</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>44550</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>44550</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>44550</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>44686</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>44817</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>44615</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44615</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>44860</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>44812</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>44526</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>44615</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         <v>44522</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>44866</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>45070</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6847,7 +6847,7 @@
         <v>45204</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         <v>45121</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>44860</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44865</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>45183</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>44580</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>45469</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>45225</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>44900</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         <v>44766</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>45469</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>45404</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         <v>45029</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>45167</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>45265</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>44903</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>45329</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>45329</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>45495</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>45495</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>45362</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>45103</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         <v>45156</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8556,7 +8556,7 @@
         <v>45103</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         <v>45103</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>44900</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         <v>45481</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         <v>45530</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>44945</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9009,7 +9009,7 @@
         <v>45359</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>45098</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>45335</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>44915</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9311,7 +9311,7 @@
         <v>45884</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>45474</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9467,7 +9467,7 @@
         <v>45105</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>44973</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>45576</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>44900</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>44958</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>45266</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>44831</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>44972</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>45576</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>45580</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>45811</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>45672</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>45006</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>45041</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>45334</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>45576</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>45485</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>45891</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>45897</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>45469</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>45358</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>44529</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>45645</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         <v>45899</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>45420</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>45904</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>45904</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>45099</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>45637</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>45904</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>45483</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>45904</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11848,7 +11848,7 @@
         <v>45904</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>44911</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>45373</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>45608</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>44546</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
         <v>44630</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         <v>45539</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>45105</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>45779</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12515,7 +12515,7 @@
         <v>45120</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>45587</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12661,7 +12661,7 @@
         <v>45608</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12734,7 +12734,7 @@
         <v>45096</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         <v>45473</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>45443</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12953,7 +12953,7 @@
         <v>45530</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13026,7 +13026,7 @@
         <v>45556</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>45469</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>45469</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>45919</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>45155</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13406,7 +13406,7 @@
         <v>45047</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13479,7 +13479,7 @@
         <v>45007</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13552,7 +13552,7 @@
         <v>44910</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>45758</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13698,7 +13698,7 @@
         <v>45790</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13771,7 +13771,7 @@
         <v>45519</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13844,7 +13844,7 @@
         <v>45531</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13917,7 +13917,7 @@
         <v>45669</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>45740</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14063,7 +14063,7 @@
         <v>45041</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14136,7 +14136,7 @@
         <v>44817</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>44900</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>45711</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         <v>45930</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>45680</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>45930</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>45687</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14662,7 +14662,7 @@
         <v>45630</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>45232</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14813,7 +14813,7 @@
         <v>45930</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>45930</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>45146</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>45547</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>45728</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>44973</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>44973</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>45212</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>45931</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>44630</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>44930</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>45594</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>45721</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>45267</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
         <v>45548</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         <v>45030</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
         <v>45204</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45594</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>45356</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>45048</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>45226</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>45937</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
         <v>45205</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         <v>45350</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16580,7 +16580,7 @@
         <v>45170</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>45232</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>44610</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>45684</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>45707</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>45623</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>44997</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>45187</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>45596</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>45280</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>45352</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>45603</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         <v>45603</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>45581</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>45090</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>45637</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>45232</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>45818</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>45477</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -17972,7 +17972,7 @@
         <v>45147</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>45013</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>45580</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
         <v>44693</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>45821</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         <v>45643</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18410,7 +18410,7 @@
         <v>45786</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>44994</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>44636</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>45758</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>45358</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18775,7 +18775,7 @@
         <v>45257</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>44973</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>45096</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>45215</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>44720</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>45784</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>45838</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>45838</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45000</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45469</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19510,7 +19510,7 @@
         <v>44685</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>45414</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19656,7 +19656,7 @@
         <v>45096</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>45594</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19802,7 +19802,7 @@
         <v>45752</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>45965</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -19953,7 +19953,7 @@
         <v>44720</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>45841</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20099,7 +20099,7 @@
         <v>45967</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>45967</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>45967</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20333,7 +20333,7 @@
         <v>45967</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20411,7 +20411,7 @@
         <v>45967</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>45967</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20567,7 +20567,7 @@
         <v>45968</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20645,7 +20645,7 @@
         <v>45967</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>45967</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20801,7 +20801,7 @@
         <v>45714</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20874,7 +20874,7 @@
         <v>45608</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>45846</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>45630</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>45265</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21166,7 +21166,7 @@
         <v>45265</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21239,7 +21239,7 @@
         <v>45258</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21312,7 +21312,7 @@
         <v>45821</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21385,7 +21385,7 @@
         <v>45669</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>45779</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>45740</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21604,7 +21604,7 @@
         <v>45314</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21677,7 +21677,7 @@
         <v>45460</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21750,7 +21750,7 @@
         <v>44973</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21823,7 +21823,7 @@
         <v>45855</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21896,7 +21896,7 @@
         <v>45473</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -21969,7 +21969,7 @@
         <v>45336</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>45861</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22120,7 +22120,7 @@
         <v>45534</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>45181</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>44783</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22349,7 +22349,7 @@
         <v>45709</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
         <v>44806</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22495,7 +22495,7 @@
         <v>45311</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22568,7 +22568,7 @@
         <v>45979</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22646,7 +22646,7 @@
         <v>45238</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22719,7 +22719,7 @@
         <v>44817</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22792,7 +22792,7 @@
         <v>45443</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
         <v>44580</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22938,7 +22938,7 @@
         <v>45282</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23011,7 +23011,7 @@
         <v>45882</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23089,7 +23089,7 @@
         <v>45981</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>45744</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>45160</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>46105</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23386,7 +23386,7 @@
         <v>45985</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23459,7 +23459,7 @@
         <v>44985</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23532,7 +23532,7 @@
         <v>44531</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>44907</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>46111</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>45469</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23834,7 +23834,7 @@
         <v>44559</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>46114</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -23980,7 +23980,7 @@
         <v>44552</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>44501</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24126,7 +24126,7 @@
         <v>44664</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24199,7 +24199,7 @@
         <v>45665</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24272,7 +24272,7 @@
         <v>46123</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24345,7 +24345,7 @@
         <v>45951</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24418,7 +24418,7 @@
         <v>45016</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24491,7 +24491,7 @@
         <v>45099</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24569,7 +24569,7 @@
         <v>44719</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24642,7 +24642,7 @@
         <v>46131</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>45258</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         <v>46006</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24866,7 +24866,7 @@
         <v>44915</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24944,7 +24944,7 @@
         <v>45875</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25017,7 +25017,7 @@
         <v>44622</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>46013</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25163,7 +25163,7 @@
         <v>46021</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25236,7 +25236,7 @@
         <v>45462</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25309,7 +25309,7 @@
         <v>45847</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25382,7 +25382,7 @@
         <v>45919</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25455,7 +25455,7 @@
         <v>44902</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25528,7 +25528,7 @@
         <v>45068</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25601,7 +25601,7 @@
         <v>45425</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25674,7 +25674,7 @@
         <v>45240</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25752,7 +25752,7 @@
         <v>46042</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25825,7 +25825,7 @@
         <v>45526</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25898,7 +25898,7 @@
         <v>45784</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25971,7 +25971,7 @@
         <v>44900</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26049,7 +26049,7 @@
         <v>46044</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>45790</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26195,7 +26195,7 @@
         <v>46043</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26268,7 +26268,7 @@
         <v>45911</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26341,7 +26341,7 @@
         <v>45120</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26414,7 +26414,7 @@
         <v>45779</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26487,7 +26487,7 @@
         <v>45530</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26560,7 +26560,7 @@
         <v>45183</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26638,7 +26638,7 @@
         <v>46051</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>46059</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>46153</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26862,7 +26862,7 @@
         <v>46153</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>46079</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>46080</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27081,7 +27081,7 @@
         <v>46080</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         <v>46084</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27227,7 +27227,7 @@
         <v>46084</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27300,7 +27300,7 @@
         <v>46084</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27373,7 +27373,7 @@
         <v>45392</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>45814</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27519,7 +27519,7 @@
         <v>45911</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27592,7 +27592,7 @@
         <v>45628</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27665,7 +27665,7 @@
         <v>46175</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27738,7 +27738,7 @@
         <v>46175</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27811,7 +27811,7 @@
         <v>46175</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>45469</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27962,7 +27962,7 @@
         <v>46181</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         <v>46181</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28108,7 +28108,7 @@
         <v>46178</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28186,7 +28186,7 @@
         <v>46191</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>46181</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28337,7 +28337,7 @@
         <v>46014</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>44881</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28488,7 +28488,7 @@
         <v>46266</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28561,7 +28561,7 @@
         <v>46099</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28634,7 +28634,7 @@
         <v>46267</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28707,7 +28707,7 @@
         <v>46273</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28780,7 +28780,7 @@
         <v>44911</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>44911</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>46279</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29009,7 +29009,7 @@
         <v>46288</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
         <v>46129</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29155,7 +29155,7 @@
         <v>46288</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29228,7 +29228,7 @@
         <v>46064</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29306,7 +29306,7 @@
         <v>46289</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29379,7 +29379,7 @@
         <v>46279</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>46290</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>46290</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29598,7 +29598,7 @@
         <v>46290</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29671,7 +29671,7 @@
         <v>46289</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29744,7 +29744,7 @@
         <v>46290</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>46251</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>46251</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>46254</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30036,7 +30036,7 @@
         <v>46303</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30109,7 +30109,7 @@
         <v>44257</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30182,7 +30182,7 @@
         <v>44607</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30260,7 +30260,7 @@
         <v>44607</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30338,7 +30338,7 @@
         <v>45930</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>

--- a/Översikt TIDAHOLM.xlsx
+++ b/Översikt TIDAHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45534</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>44637</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>44902</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>46262</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>43986</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44607</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>45183</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>44930</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>46279</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44607</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>44512</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>44512</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>44865</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>45246</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>45232</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45899</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>45925</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45930</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>46055</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>45684</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>44637</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>46289</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>45322</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44607</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>44607</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>44607</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>46064</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>44519</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>44573</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>44783</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>44508</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44529</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>44550</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>44832</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>44594</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>44630</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>44615</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>44508</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44694</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>44512</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>44587</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>44889</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>44783</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>44546</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>44573</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>44703</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>44613</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>44869</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>44526</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>44615</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>44623</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>44686</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>44615</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>44615</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>44522</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>44589</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>44615</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>44588</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>44511</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>44550</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44550</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>44550</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>44860</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>44812</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>44817</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         <v>44580</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>44719</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>45534</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>45425</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>44693</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>45266</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>45267</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>45758</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>44559</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>44903</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>45483</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>44900</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>44817</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>45099</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>45099</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>45103</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>45643</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>45721</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>45580</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>44610</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>45120</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>45041</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>45016</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>45167</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>45481</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>44860</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>45420</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>45314</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>45103</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>45335</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>45232</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>45687</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>44636</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>45637</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>45068</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>45204</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>45443</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>45637</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>44831</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>44720</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>45623</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>45215</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>45212</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>45359</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>45548</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>45183</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>45105</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>45280</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>45336</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>45146</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>45356</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>45581</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>45882</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10547,7 +10547,7 @@
         <v>45784</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>45884</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>45103</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>45875</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>45672</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>44945</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>45556</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>44817</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>45811</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>45669</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>45919</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>45891</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>45911</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>44783</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>45897</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>45899</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>45779</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>45790</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>44622</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>45847</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>45232</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>45904</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>45904</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v>45904</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>45904</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>45904</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12485,7 +12485,7 @@
         <v>45098</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>45462</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
         <v>45919</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>45006</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>45630</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>44900</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>45608</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>45665</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>45930</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>45930</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>45930</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>45930</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13391,7 +13391,7 @@
         <v>45931</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13464,7 +13464,7 @@
         <v>46153</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>46153</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>45477</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13683,7 +13683,7 @@
         <v>45937</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13756,7 +13756,7 @@
         <v>45576</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
         <v>45282</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>45474</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         <v>45121</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>45580</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14131,7 +14131,7 @@
         <v>44900</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>45709</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14282,7 +14282,7 @@
         <v>45358</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
         <v>45358</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>45576</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>45965</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>45156</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         <v>45967</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14730,7 +14730,7 @@
         <v>45814</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>45539</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>45967</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14954,7 +14954,7 @@
         <v>45967</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15032,7 +15032,7 @@
         <v>45967</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>45967</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         <v>45967</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>45967</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15344,7 +15344,7 @@
         <v>45967</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         <v>44973</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>45392</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>44580</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>45968</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>45232</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>45979</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>45105</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>45981</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>45911</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>45030</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>45985</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>45469</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>45469</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>45469</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16479,7 +16479,7 @@
         <v>44529</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16552,7 +16552,7 @@
         <v>45362</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16625,7 +16625,7 @@
         <v>44973</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>44806</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>45596</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>45352</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>45603</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         <v>45603</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>45530</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         <v>45443</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>45951</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17282,7 +17282,7 @@
         <v>44630</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
         <v>46006</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>45530</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17506,7 +17506,7 @@
         <v>44910</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         <v>45594</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>46013</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17725,7 +17725,7 @@
         <v>45628</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>45096</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17871,7 +17871,7 @@
         <v>46021</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17944,7 +17944,7 @@
         <v>46175</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>46175</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>45414</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>44552</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18236,7 +18236,7 @@
         <v>46175</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>45469</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>45240</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>46178</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>46043</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         <v>46042</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>46044</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>45469</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>46181</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>44546</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>46181</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>46051</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>46059</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19210,7 +19210,7 @@
         <v>45404</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>45048</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>45000</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>45013</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19502,7 +19502,7 @@
         <v>44685</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19575,7 +19575,7 @@
         <v>45047</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19648,7 +19648,7 @@
         <v>45204</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>46080</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>45469</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
         <v>45469</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>46079</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>45311</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>46080</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>46084</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>46084</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>46084</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>44958</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>45147</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>45576</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20607,7 +20607,7 @@
         <v>44930</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20680,7 +20680,7 @@
         <v>46191</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>46181</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20831,7 +20831,7 @@
         <v>44973</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20909,7 +20909,7 @@
         <v>44915</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20987,7 +20987,7 @@
         <v>44915</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>46105</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>44911</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21216,7 +21216,7 @@
         <v>46111</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21289,7 +21289,7 @@
         <v>46114</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21362,7 +21362,7 @@
         <v>44501</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>44972</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21508,7 +21508,7 @@
         <v>46123</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21581,7 +21581,7 @@
         <v>44766</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>45594</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>46131</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21800,7 +21800,7 @@
         <v>46014</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>45238</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>45373</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>44865</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45526</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>45070</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>45155</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44900</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22399,7 +22399,7 @@
         <v>45225</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22472,7 +22472,7 @@
         <v>45587</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         <v>45007</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22618,7 +22618,7 @@
         <v>44985</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>45257</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22764,7 +22764,7 @@
         <v>44900</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         <v>45485</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>46099</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22988,7 +22988,7 @@
         <v>44881</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23061,7 +23061,7 @@
         <v>45160</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>46273</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23207,7 +23207,7 @@
         <v>45714</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>44973</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>44973</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>45744</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>44907</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>45758</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>44911</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23723,7 +23723,7 @@
         <v>46279</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23796,7 +23796,7 @@
         <v>45334</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>44911</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>45684</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>45029</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>45469</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>44902</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>45265</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24317,7 +24317,7 @@
         <v>44994</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>45707</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>45608</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24536,7 +24536,7 @@
         <v>44866</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24609,7 +24609,7 @@
         <v>44720</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24682,7 +24682,7 @@
         <v>46129</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24755,7 +24755,7 @@
         <v>45205</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>45181</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>44630</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>45329</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>45329</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>45120</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25193,7 +25193,7 @@
         <v>46289</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>45645</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>46289</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>46279</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>46288</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25558,7 +25558,7 @@
         <v>45096</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25631,7 +25631,7 @@
         <v>46288</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>45594</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25777,7 +25777,7 @@
         <v>45630</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25850,7 +25850,7 @@
         <v>45258</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25923,7 +25923,7 @@
         <v>46290</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>45041</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         <v>45187</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>46290</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26215,7 +26215,7 @@
         <v>46290</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26288,7 +26288,7 @@
         <v>46064</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>45495</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>45495</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26512,7 +26512,7 @@
         <v>46290</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>45226</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26658,7 +26658,7 @@
         <v>45090</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>46251</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         <v>46251</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>45183</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26955,7 +26955,7 @@
         <v>45265</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27028,7 +27028,7 @@
         <v>45265</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27101,7 +27101,7 @@
         <v>44531</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27179,7 +27179,7 @@
         <v>46254</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27252,7 +27252,7 @@
         <v>45752</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27325,7 +27325,7 @@
         <v>44664</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27398,7 +27398,7 @@
         <v>45547</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         <v>45779</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27549,7 +27549,7 @@
         <v>45608</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>45473</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>45530</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
         <v>45531</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>45740</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>46303</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>45711</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>45519</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>45790</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>45680</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28279,7 +28279,7 @@
         <v>45728</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>45170</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>46266</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>45350</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>44997</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>46267</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>45818</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>45786</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28863,7 +28863,7 @@
         <v>45821</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>45096</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29009,7 +29009,7 @@
         <v>45784</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
         <v>45838</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29155,7 +29155,7 @@
         <v>45838</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29228,7 +29228,7 @@
         <v>45841</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>45779</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>45669</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29447,7 +29447,7 @@
         <v>45258</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>45846</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>45740</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>45821</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>45460</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>45855</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>45473</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>45861</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30036,7 +30036,7 @@
         <v>44257</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30109,7 +30109,7 @@
         <v>44607</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>44607</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>45930</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>

--- a/Översikt TIDAHOLM.xlsx
+++ b/Översikt TIDAHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45534</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>44637</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>44902</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>46262</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>43986</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44607</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>45183</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>44930</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>46279</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44607</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>44512</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>44512</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>44865</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>45246</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2362,7 +2362,7 @@
         <v>45232</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45899</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2577,7 +2577,7 @@
         <v>45925</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         <v>45930</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>46055</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2901,7 +2901,7 @@
         <v>45684</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>44637</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3116,7 +3116,7 @@
         <v>46289</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>45322</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>44607</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>44607</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>44607</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>46064</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>44519</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         <v>44573</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>44783</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4063,7 +4063,7 @@
         <v>44508</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>44529</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>44550</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>44832</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
         <v>44594</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>44630</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>44615</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4574,7 +4574,7 @@
         <v>44508</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44694</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4720,7 +4720,7 @@
         <v>44512</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>44587</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>44889</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>44783</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>44546</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         <v>44573</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>44703</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>44613</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>44869</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>44526</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>44615</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>44623</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>44686</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>44615</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>44615</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>44522</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>44589</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>44615</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>44588</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>44511</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
         <v>44550</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44550</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         <v>44550</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         <v>44860</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         <v>44812</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         <v>44817</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6628,7 +6628,7 @@
         <v>44580</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6701,7 +6701,7 @@
         <v>44719</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6774,7 +6774,7 @@
         <v>45534</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>45425</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>44693</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>45266</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>45267</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>45758</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>44559</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>44903</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>45483</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>44900</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>44817</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>45099</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>45099</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>45103</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>45643</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7894,7 +7894,7 @@
         <v>45721</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         <v>45580</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>44610</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>45120</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8186,7 +8186,7 @@
         <v>45041</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
         <v>45016</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>45167</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
         <v>45481</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8478,7 +8478,7 @@
         <v>44860</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>45420</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         <v>45314</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8697,7 +8697,7 @@
         <v>45103</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         <v>45335</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>45232</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>45687</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>44636</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>45637</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9145,7 +9145,7 @@
         <v>45068</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         <v>45204</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9291,7 +9291,7 @@
         <v>45443</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>45637</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         <v>44831</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>44720</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9583,7 +9583,7 @@
         <v>45623</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9656,7 +9656,7 @@
         <v>45215</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>45212</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>45359</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>45548</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>45183</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>45105</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>45280</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>45336</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>45146</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>45356</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>45581</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10469,7 +10469,7 @@
         <v>45882</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10547,7 +10547,7 @@
         <v>45784</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>45884</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10698,7 +10698,7 @@
         <v>45103</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>45875</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>45672</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10922,7 +10922,7 @@
         <v>44945</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>45556</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>44817</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>45811</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>45669</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11287,7 +11287,7 @@
         <v>45919</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
         <v>45891</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>45911</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11506,7 +11506,7 @@
         <v>44783</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11584,7 +11584,7 @@
         <v>45897</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>45899</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>45779</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>45790</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>44622</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>45847</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>45232</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>45904</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>45904</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v>45904</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>45904</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>45904</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12485,7 +12485,7 @@
         <v>45098</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12563,7 +12563,7 @@
         <v>45462</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
         <v>45919</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>45006</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12782,7 +12782,7 @@
         <v>45630</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12855,7 +12855,7 @@
         <v>44900</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>45608</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>45665</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>45930</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>45930</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>45930</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>45930</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13391,7 +13391,7 @@
         <v>45931</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13464,7 +13464,7 @@
         <v>46153</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>46153</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>45477</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13683,7 +13683,7 @@
         <v>45937</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13756,7 +13756,7 @@
         <v>45576</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
         <v>45282</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>45474</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -13980,7 +13980,7 @@
         <v>45121</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14058,7 +14058,7 @@
         <v>45580</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14131,7 +14131,7 @@
         <v>44900</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>45709</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14282,7 +14282,7 @@
         <v>45358</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14355,7 +14355,7 @@
         <v>45358</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>45576</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>45965</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>45156</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         <v>45967</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14730,7 +14730,7 @@
         <v>45814</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>45539</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14876,7 +14876,7 @@
         <v>45967</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -14954,7 +14954,7 @@
         <v>45967</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15032,7 +15032,7 @@
         <v>45967</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15110,7 +15110,7 @@
         <v>45967</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         <v>45967</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>45967</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15344,7 +15344,7 @@
         <v>45967</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         <v>44973</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15495,7 +15495,7 @@
         <v>45392</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
         <v>44580</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15641,7 +15641,7 @@
         <v>45968</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15719,7 +15719,7 @@
         <v>45232</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15797,7 +15797,7 @@
         <v>45979</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15875,7 +15875,7 @@
         <v>45105</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         <v>45981</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16026,7 +16026,7 @@
         <v>45911</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>45030</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16172,7 +16172,7 @@
         <v>45985</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16245,7 +16245,7 @@
         <v>45469</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16323,7 +16323,7 @@
         <v>45469</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16401,7 +16401,7 @@
         <v>45469</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16479,7 +16479,7 @@
         <v>44529</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16552,7 +16552,7 @@
         <v>45362</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16625,7 +16625,7 @@
         <v>44973</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>44806</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>45596</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>45352</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>45603</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         <v>45603</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>45530</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17136,7 +17136,7 @@
         <v>45443</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>45951</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17282,7 +17282,7 @@
         <v>44630</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
         <v>46006</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>45530</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17506,7 +17506,7 @@
         <v>44910</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         <v>45594</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>46013</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17725,7 +17725,7 @@
         <v>45628</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>45096</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17871,7 +17871,7 @@
         <v>46021</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17944,7 +17944,7 @@
         <v>46175</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18017,7 +18017,7 @@
         <v>46175</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>45414</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18163,7 +18163,7 @@
         <v>44552</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18236,7 +18236,7 @@
         <v>46175</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>45469</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18387,7 +18387,7 @@
         <v>45240</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>46178</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18543,7 +18543,7 @@
         <v>46043</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         <v>46042</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>46044</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18762,7 +18762,7 @@
         <v>45469</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>46181</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>44546</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -18986,7 +18986,7 @@
         <v>46181</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>46051</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19137,7 +19137,7 @@
         <v>46059</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19210,7 +19210,7 @@
         <v>45404</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>45048</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>45000</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>45013</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19502,7 +19502,7 @@
         <v>44685</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19575,7 +19575,7 @@
         <v>45047</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19648,7 +19648,7 @@
         <v>45204</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>46080</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19794,7 +19794,7 @@
         <v>45469</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
         <v>45469</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>46079</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>45311</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>46080</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>46084</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>46084</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20315,7 +20315,7 @@
         <v>46084</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20388,7 +20388,7 @@
         <v>44958</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>45147</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>45576</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20607,7 +20607,7 @@
         <v>44930</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20680,7 +20680,7 @@
         <v>46191</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>46181</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20831,7 +20831,7 @@
         <v>44973</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20909,7 +20909,7 @@
         <v>44915</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -20987,7 +20987,7 @@
         <v>44915</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>46105</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21138,7 +21138,7 @@
         <v>44911</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21216,7 +21216,7 @@
         <v>46111</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21289,7 +21289,7 @@
         <v>46114</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21362,7 +21362,7 @@
         <v>44501</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>44972</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21508,7 +21508,7 @@
         <v>46123</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21581,7 +21581,7 @@
         <v>44766</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>45594</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>46131</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21800,7 +21800,7 @@
         <v>46014</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>45238</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>45373</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22024,7 +22024,7 @@
         <v>44865</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22097,7 +22097,7 @@
         <v>45526</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>45070</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>45155</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44900</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22399,7 +22399,7 @@
         <v>45225</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22472,7 +22472,7 @@
         <v>45587</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         <v>45007</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22618,7 +22618,7 @@
         <v>44985</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>45257</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22764,7 +22764,7 @@
         <v>44900</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         <v>45485</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>46099</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -22988,7 +22988,7 @@
         <v>44881</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23061,7 +23061,7 @@
         <v>45160</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23134,7 +23134,7 @@
         <v>46273</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23207,7 +23207,7 @@
         <v>45714</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>44973</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>44973</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>45744</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>44907</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>45758</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>44911</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23723,7 +23723,7 @@
         <v>46279</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23796,7 +23796,7 @@
         <v>45334</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>44911</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>45684</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>45029</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>45469</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24171,7 +24171,7 @@
         <v>44902</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>45265</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24317,7 +24317,7 @@
         <v>44994</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>45707</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>45608</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24536,7 +24536,7 @@
         <v>44866</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24609,7 +24609,7 @@
         <v>44720</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24682,7 +24682,7 @@
         <v>46129</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24755,7 +24755,7 @@
         <v>45205</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>45181</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>44630</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>45329</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>45329</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>45120</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25193,7 +25193,7 @@
         <v>46289</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>45645</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>46289</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>46279</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>46288</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25558,7 +25558,7 @@
         <v>45096</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25631,7 +25631,7 @@
         <v>46288</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>45594</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25777,7 +25777,7 @@
         <v>45630</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25850,7 +25850,7 @@
         <v>45258</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25923,7 +25923,7 @@
         <v>46290</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>45041</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         <v>45187</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>46290</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26215,7 +26215,7 @@
         <v>46290</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26288,7 +26288,7 @@
         <v>46064</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26366,7 +26366,7 @@
         <v>45495</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26439,7 +26439,7 @@
         <v>45495</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26512,7 +26512,7 @@
         <v>46290</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26585,7 +26585,7 @@
         <v>45226</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26658,7 +26658,7 @@
         <v>45090</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>46251</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26804,7 +26804,7 @@
         <v>46251</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>45183</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -26955,7 +26955,7 @@
         <v>45265</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27028,7 +27028,7 @@
         <v>45265</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27101,7 +27101,7 @@
         <v>44531</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27179,7 +27179,7 @@
         <v>46254</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27252,7 +27252,7 @@
         <v>45752</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27325,7 +27325,7 @@
         <v>44664</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27398,7 +27398,7 @@
         <v>45547</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27476,7 +27476,7 @@
         <v>45779</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27549,7 +27549,7 @@
         <v>45608</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27622,7 +27622,7 @@
         <v>45473</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27695,7 +27695,7 @@
         <v>45530</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
         <v>45531</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27841,7 +27841,7 @@
         <v>45740</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27914,7 +27914,7 @@
         <v>46303</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -27987,7 +27987,7 @@
         <v>45711</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>45519</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28133,7 +28133,7 @@
         <v>45790</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28206,7 +28206,7 @@
         <v>45680</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28279,7 +28279,7 @@
         <v>45728</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>45170</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28425,7 +28425,7 @@
         <v>46266</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28498,7 +28498,7 @@
         <v>45350</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>44997</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>46267</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>45818</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28790,7 +28790,7 @@
         <v>45786</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28863,7 +28863,7 @@
         <v>45821</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
         <v>45096</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29009,7 +29009,7 @@
         <v>45784</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
         <v>45838</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29155,7 +29155,7 @@
         <v>45838</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29228,7 +29228,7 @@
         <v>45841</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>45779</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>45669</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29447,7 +29447,7 @@
         <v>45258</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>45846</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>45740</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>45821</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29739,7 +29739,7 @@
         <v>45460</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29812,7 +29812,7 @@
         <v>45855</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29885,7 +29885,7 @@
         <v>45473</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>45861</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30036,7 +30036,7 @@
         <v>44257</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30109,7 +30109,7 @@
         <v>44607</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>44607</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>45930</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>

--- a/Översikt TIDAHOLM.xlsx
+++ b/Översikt TIDAHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45534</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>44637</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>44902</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>46262</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>43986</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44607</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>46279</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>44930</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>45183</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44607</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>44512</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>44512</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>44865</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>45322</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>45899</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>45925</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>45930</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>44637</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>45684</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>46055</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>46289</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>46315</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>45246</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>45232</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>44607</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>44607</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>44607</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>46064</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>44519</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>44573</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>44529</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>44550</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>44832</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>44594</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         <v>44630</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>44615</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>44508</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>44694</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>44512</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>44587</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>44889</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>44783</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>44546</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>44573</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>44703</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>44869</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>44613</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>44526</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>44615</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>44623</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>44686</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>44615</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
         <v>44615</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>44522</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>44589</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>44615</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>44588</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>44511</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>44550</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44550</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>44550</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44860</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>44812</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>44817</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>44580</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>45811</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>45672</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>45329</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>45329</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>45891</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>45359</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>45897</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>45098</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>45335</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         <v>44866</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>45899</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>45904</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>45904</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>45904</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>45204</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>45904</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>45904</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>44860</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>45462</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>44902</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>45068</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>45425</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         <v>45919</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>45911</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>44900</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>45930</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>45930</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>45930</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>45930</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>45628</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>45931</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>45120</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>46175</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         <v>45530</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         <v>45937</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         <v>45183</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>45265</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45121</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>45183</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>45469</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
         <v>45225</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>46175</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>46175</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>44766</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>45469</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>45469</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
         <v>45404</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>44900</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>45530</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>44945</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         <v>46181</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>46181</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>46178</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
         <v>45103</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>45156</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>45481</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>46191</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>45965</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>45967</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11233,7 +11233,7 @@
         <v>45967</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>45967</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>45967</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>45967</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>45967</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>45968</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>45967</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
         <v>45967</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
         <v>46181</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>45105</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>44900</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>45474</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>45979</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>44972</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>45576</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>45580</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>45981</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>44973</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>45041</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>46014</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>45985</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>45358</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>45645</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>45576</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>45637</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>45951</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>44881</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>46099</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>46006</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13430,7 +13430,7 @@
         <v>45779</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>45608</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>44911</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>44911</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>45473</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>44958</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>45530</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>46013</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>46279</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>46021</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>45790</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>45519</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>45531</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>45740</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>45711</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>45680</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         <v>45728</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>45240</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>46042</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>46288</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>46044</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>46129</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>46288</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>46043</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>46064</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>46289</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>46279</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>46290</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>46290</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>46290</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>46289</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>46290</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>45350</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>45170</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>46051</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>46059</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>44997</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>45818</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
         <v>46251</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>45821</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>46079</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>45786</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>46080</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>46080</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>46084</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>46084</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>45096</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>46084</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>46251</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>45784</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>45838</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>45838</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>46254</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>45841</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>45334</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>45485</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>45846</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>45258</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>45821</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>45669</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>46105</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>45779</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>45469</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>45740</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>44529</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>45460</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>45855</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>45473</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>46111</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>45861</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>46114</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>45420</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>46123</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>45099</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18872,7 +18872,7 @@
         <v>45483</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         <v>46131</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19018,7 +19018,7 @@
         <v>45882</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19096,7 +19096,7 @@
         <v>44911</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19174,7 +19174,7 @@
         <v>45884</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>44630</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19325,7 +19325,7 @@
         <v>45539</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19398,7 +19398,7 @@
         <v>45587</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
         <v>45875</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19544,7 +19544,7 @@
         <v>45556</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19617,7 +19617,7 @@
         <v>44622</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>46267</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19763,7 +19763,7 @@
         <v>46266</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>45847</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>45919</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19982,7 +19982,7 @@
         <v>45007</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>44910</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>45041</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20201,7 +20201,7 @@
         <v>44900</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         <v>45526</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>45784</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>45687</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>46273</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>45790</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>45232</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>46303</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>45146</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>45911</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>45779</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45547</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>46315</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>44973</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>44973</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>45212</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>46315</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>46315</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>44630</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>44930</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>46315</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>45594</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45548</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>45048</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>45226</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>46153</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>45684</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>45707</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>46153</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45596</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>45280</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>45352</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>45603</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>45603</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>45581</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>45392</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>45477</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>45814</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>45013</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23078,7 +23078,7 @@
         <v>45580</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>45643</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>44994</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>44973</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>45000</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23443,7 +23443,7 @@
         <v>45469</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>45414</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>45096</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
         <v>45594</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>45608</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>45630</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>45534</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>45181</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>44783</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>45709</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>44817</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>45443</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>44580</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>45744</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>44531</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>44559</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>45070</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24704,7 +24704,7 @@
         <v>44865</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>44900</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24855,7 +24855,7 @@
         <v>45029</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24928,7 +24928,7 @@
         <v>45167</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>44903</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>45495</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>45495</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45362</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>45103</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>45103</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>44915</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25527,7 +25527,7 @@
         <v>45266</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44831</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>45006</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25746,7 +25746,7 @@
         <v>45576</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25819,7 +25819,7 @@
         <v>45373</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>45608</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>44546</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45105</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>45120</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>45096</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>45443</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26330,7 +26330,7 @@
         <v>45469</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>45469</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>45155</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>45047</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>45758</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>45669</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>44817</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26856,7 +26856,7 @@
         <v>45630</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>45721</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27002,7 +27002,7 @@
         <v>45267</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27075,7 +27075,7 @@
         <v>45030</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27148,7 +27148,7 @@
         <v>45204</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27221,7 +27221,7 @@
         <v>45594</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27294,7 +27294,7 @@
         <v>45356</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27367,7 +27367,7 @@
         <v>45205</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>45232</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27518,7 +27518,7 @@
         <v>44610</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>45623</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>45187</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>45090</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>45637</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>45232</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27956,7 +27956,7 @@
         <v>45147</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28029,7 +28029,7 @@
         <v>44693</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         <v>44636</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28175,7 +28175,7 @@
         <v>45758</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>45358</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>45257</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28394,7 +28394,7 @@
         <v>45215</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>44720</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>44685</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>45752</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28686,7 +28686,7 @@
         <v>44720</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28759,7 +28759,7 @@
         <v>45714</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28832,7 +28832,7 @@
         <v>45265</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>45265</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28978,7 +28978,7 @@
         <v>45314</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29051,7 +29051,7 @@
         <v>44973</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>45336</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29197,7 +29197,7 @@
         <v>44806</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>45311</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29343,7 +29343,7 @@
         <v>45238</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>45282</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29489,7 +29489,7 @@
         <v>45160</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29562,7 +29562,7 @@
         <v>44985</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29635,7 +29635,7 @@
         <v>44907</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29708,7 +29708,7 @@
         <v>45469</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>44552</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29859,7 +29859,7 @@
         <v>44501</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>44664</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30005,7 +30005,7 @@
         <v>45665</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30078,7 +30078,7 @@
         <v>45016</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30151,7 +30151,7 @@
         <v>45099</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
         <v>44719</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30302,7 +30302,7 @@
         <v>45258</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>44915</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30453,7 +30453,7 @@
         <v>44257</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>44607</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30604,7 +30604,7 @@
         <v>44607</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30682,7 +30682,7 @@
         <v>45930</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>

--- a/Översikt TIDAHOLM.xlsx
+++ b/Översikt TIDAHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>45534</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
         <v>44637</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -835,7 +835,7 @@
         <v>44902</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
         <v>44607</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1065,7 +1065,7 @@
         <v>46262</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>45310</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>43986</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>44607</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>46279</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>44930</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>45183</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>44607</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1937,7 +1937,7 @@
         <v>44512</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>44512</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>44865</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
         <v>45322</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>45899</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         <v>45925</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         <v>45930</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>44637</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2791,7 +2791,7 @@
         <v>45684</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>46055</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>46289</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>46315</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>45246</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3326,7 +3326,7 @@
         <v>45232</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>44607</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>44607</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>44607</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>46064</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
         <v>44519</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
         <v>44573</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>44783</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         <v>44783</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4173,7 +4173,7 @@
         <v>44508</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>44529</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4319,7 +4319,7 @@
         <v>44550</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4392,7 +4392,7 @@
         <v>44832</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>44594</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         <v>44630</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         <v>44615</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -4684,7 +4684,7 @@
         <v>44508</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>44694</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>44512</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         <v>44587</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>44889</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>44783</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>44546</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
         <v>44573</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5273,7 +5273,7 @@
         <v>44703</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>44869</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         <v>44613</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         <v>44526</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>44615</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>44623</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>44686</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>44615</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -5862,7 +5862,7 @@
         <v>44615</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         <v>44522</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>44589</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         <v>44615</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>44588</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>44511</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>44550</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6373,7 +6373,7 @@
         <v>44550</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>44550</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6519,7 +6519,7 @@
         <v>44860</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6592,7 +6592,7 @@
         <v>44812</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -6665,7 +6665,7 @@
         <v>44817</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6738,7 +6738,7 @@
         <v>44580</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6811,7 +6811,7 @@
         <v>45811</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>45672</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>45329</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         <v>45329</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>45891</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>45359</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>45897</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>45098</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>45335</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         <v>44866</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>45899</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>45904</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -7697,7 +7697,7 @@
         <v>45904</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>45904</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>45204</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>45904</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         <v>45904</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8082,7 +8082,7 @@
         <v>44860</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>45462</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         <v>44902</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>45068</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>45425</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         <v>45919</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8520,7 +8520,7 @@
         <v>45911</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8593,7 +8593,7 @@
         <v>44900</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -8671,7 +8671,7 @@
         <v>45930</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
         <v>45930</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>45930</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -8905,7 +8905,7 @@
         <v>45930</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>45628</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9056,7 +9056,7 @@
         <v>45931</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>45120</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>46175</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9275,7 +9275,7 @@
         <v>45530</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9348,7 +9348,7 @@
         <v>45937</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         <v>45183</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9499,7 +9499,7 @@
         <v>45265</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9572,7 +9572,7 @@
         <v>45121</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>45183</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>45469</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
         <v>45225</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>46175</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>46175</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>44766</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>45469</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10176,7 +10176,7 @@
         <v>45469</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
         <v>45404</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         <v>44900</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>45530</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>44945</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10551,7 +10551,7 @@
         <v>46181</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>46181</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
         <v>46178</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
         <v>45103</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>45156</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>45481</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>46191</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>45965</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11155,7 +11155,7 @@
         <v>45967</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11233,7 +11233,7 @@
         <v>45967</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>45967</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11389,7 +11389,7 @@
         <v>45967</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11467,7 +11467,7 @@
         <v>45967</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>45967</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11623,7 +11623,7 @@
         <v>45968</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>45967</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
         <v>45967</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
         <v>46181</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>45105</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>44900</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12086,7 +12086,7 @@
         <v>45474</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12164,7 +12164,7 @@
         <v>45979</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>44972</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>45576</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>45580</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>45981</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>44973</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         <v>45041</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12690,7 +12690,7 @@
         <v>46014</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -12768,7 +12768,7 @@
         <v>45985</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>45358</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -12914,7 +12914,7 @@
         <v>45645</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
         <v>45576</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>45637</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13133,7 +13133,7 @@
         <v>45951</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         <v>44881</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13279,7 +13279,7 @@
         <v>46099</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>46006</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13430,7 +13430,7 @@
         <v>45779</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>45608</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>44911</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>44911</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>45473</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -13805,7 +13805,7 @@
         <v>44958</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -13878,7 +13878,7 @@
         <v>45530</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -13951,7 +13951,7 @@
         <v>46013</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>46279</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14097,7 +14097,7 @@
         <v>46021</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14170,7 +14170,7 @@
         <v>45790</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>45519</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>45531</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>45740</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14462,7 +14462,7 @@
         <v>45711</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14535,7 +14535,7 @@
         <v>45680</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14608,7 +14608,7 @@
         <v>45728</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>45240</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -14759,7 +14759,7 @@
         <v>46042</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         <v>46288</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -14905,7 +14905,7 @@
         <v>46044</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -14978,7 +14978,7 @@
         <v>46129</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>46288</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>46043</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15197,7 +15197,7 @@
         <v>46064</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>46289</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15348,7 +15348,7 @@
         <v>46279</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15421,7 +15421,7 @@
         <v>46290</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>46290</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15567,7 +15567,7 @@
         <v>46290</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>46289</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
         <v>46290</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -15786,7 +15786,7 @@
         <v>45350</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>45170</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>46051</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16010,7 +16010,7 @@
         <v>46059</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16083,7 +16083,7 @@
         <v>44997</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16156,7 +16156,7 @@
         <v>45818</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16229,7 +16229,7 @@
         <v>46251</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16302,7 +16302,7 @@
         <v>45821</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>46079</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>45786</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>46080</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16594,7 +16594,7 @@
         <v>46080</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16667,7 +16667,7 @@
         <v>46084</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>46084</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -16813,7 +16813,7 @@
         <v>45096</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>46084</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>46251</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17032,7 +17032,7 @@
         <v>45784</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>45838</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17178,7 +17178,7 @@
         <v>45838</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>46254</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>45841</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17397,7 +17397,7 @@
         <v>45334</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17470,7 +17470,7 @@
         <v>45485</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>45846</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>45258</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -17689,7 +17689,7 @@
         <v>45821</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -17762,7 +17762,7 @@
         <v>45669</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>46105</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>45779</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -17981,7 +17981,7 @@
         <v>45469</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>45740</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>44529</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18205,7 +18205,7 @@
         <v>45460</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
         <v>45855</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>45473</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18424,7 +18424,7 @@
         <v>46111</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>45861</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>46114</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>45420</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -18721,7 +18721,7 @@
         <v>46123</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -18794,7 +18794,7 @@
         <v>45099</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -18872,7 +18872,7 @@
         <v>45483</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         <v>46131</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19018,7 +19018,7 @@
         <v>45882</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19096,7 +19096,7 @@
         <v>44911</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19174,7 +19174,7 @@
         <v>45884</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19252,7 +19252,7 @@
         <v>44630</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19325,7 +19325,7 @@
         <v>45539</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19398,7 +19398,7 @@
         <v>45587</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19471,7 +19471,7 @@
         <v>45875</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19544,7 +19544,7 @@
         <v>45556</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19617,7 +19617,7 @@
         <v>44622</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>46267</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -19763,7 +19763,7 @@
         <v>46266</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>45847</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>45919</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -19982,7 +19982,7 @@
         <v>45007</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>44910</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>45041</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20201,7 +20201,7 @@
         <v>44900</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20279,7 +20279,7 @@
         <v>45526</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>45784</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>45687</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>46273</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20571,7 +20571,7 @@
         <v>45790</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>45232</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>46303</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>45146</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>45911</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>45779</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45547</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>46315</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>44973</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>44973</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>45212</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>46315</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21462,7 +21462,7 @@
         <v>46315</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21540,7 +21540,7 @@
         <v>44630</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>44930</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>46315</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>45594</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>45548</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>45048</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>45226</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22056,7 +22056,7 @@
         <v>46153</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>45684</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>45707</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22275,7 +22275,7 @@
         <v>46153</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22348,7 +22348,7 @@
         <v>45596</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>45280</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22494,7 +22494,7 @@
         <v>45352</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22567,7 +22567,7 @@
         <v>45603</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>45603</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -22713,7 +22713,7 @@
         <v>45581</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -22786,7 +22786,7 @@
         <v>45392</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -22859,7 +22859,7 @@
         <v>45477</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -22932,7 +22932,7 @@
         <v>45814</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>45013</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23078,7 +23078,7 @@
         <v>45580</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23151,7 +23151,7 @@
         <v>45643</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>44994</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>44973</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23370,7 +23370,7 @@
         <v>45000</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23443,7 +23443,7 @@
         <v>45469</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23521,7 +23521,7 @@
         <v>45414</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23594,7 +23594,7 @@
         <v>45096</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -23667,7 +23667,7 @@
         <v>45594</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -23740,7 +23740,7 @@
         <v>45608</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>45630</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -23886,7 +23886,7 @@
         <v>45534</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -23964,7 +23964,7 @@
         <v>45181</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>44783</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24115,7 +24115,7 @@
         <v>45709</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>44817</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>45443</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>44580</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>45744</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>44531</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>44559</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24631,7 +24631,7 @@
         <v>45070</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -24704,7 +24704,7 @@
         <v>44865</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -24777,7 +24777,7 @@
         <v>44900</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -24855,7 +24855,7 @@
         <v>45029</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -24928,7 +24928,7 @@
         <v>45167</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>44903</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>45495</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>45495</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25220,7 +25220,7 @@
         <v>45362</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>45103</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25371,7 +25371,7 @@
         <v>45103</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25449,7 +25449,7 @@
         <v>44915</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25527,7 +25527,7 @@
         <v>45266</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25600,7 +25600,7 @@
         <v>44831</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>45006</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -25746,7 +25746,7 @@
         <v>45576</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -25819,7 +25819,7 @@
         <v>45373</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>45608</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>44546</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>45105</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>45120</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>45096</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>45443</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26330,7 +26330,7 @@
         <v>45469</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26408,7 +26408,7 @@
         <v>45469</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>45155</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>45047</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>45758</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>45669</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>44817</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -26856,7 +26856,7 @@
         <v>45630</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>45721</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27002,7 +27002,7 @@
         <v>45267</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27075,7 +27075,7 @@
         <v>45030</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27148,7 +27148,7 @@
         <v>45204</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27221,7 +27221,7 @@
         <v>45594</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27294,7 +27294,7 @@
         <v>45356</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27367,7 +27367,7 @@
         <v>45205</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>45232</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27518,7 +27518,7 @@
         <v>44610</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>45623</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>45187</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>45090</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>45637</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>45232</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -27956,7 +27956,7 @@
         <v>45147</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28029,7 +28029,7 @@
         <v>44693</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         <v>44636</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28175,7 +28175,7 @@
         <v>45758</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>45358</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28321,7 +28321,7 @@
         <v>45257</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28394,7 +28394,7 @@
         <v>45215</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>44720</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>44685</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>45752</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28686,7 +28686,7 @@
         <v>44720</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -28759,7 +28759,7 @@
         <v>45714</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -28832,7 +28832,7 @@
         <v>45265</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -28905,7 +28905,7 @@
         <v>45265</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -28978,7 +28978,7 @@
         <v>45314</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29051,7 +29051,7 @@
         <v>44973</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29124,7 +29124,7 @@
         <v>45336</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29197,7 +29197,7 @@
         <v>44806</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29270,7 +29270,7 @@
         <v>45311</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29343,7 +29343,7 @@
         <v>45238</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>45282</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29489,7 +29489,7 @@
         <v>45160</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29562,7 +29562,7 @@
         <v>44985</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29635,7 +29635,7 @@
         <v>44907</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -29708,7 +29708,7 @@
         <v>45469</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -29786,7 +29786,7 @@
         <v>44552</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -29859,7 +29859,7 @@
         <v>44501</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>44664</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30005,7 +30005,7 @@
         <v>45665</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30078,7 +30078,7 @@
         <v>45016</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30151,7 +30151,7 @@
         <v>45099</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
         <v>44719</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30302,7 +30302,7 @@
         <v>45258</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>44915</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30453,7 +30453,7 @@
         <v>44257</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>44607</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30604,7 +30604,7 @@
         <v>44607</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30682,7 +30682,7 @@
         <v>45930</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
